--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IDC e Normalizados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Componentes Brutos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDC e Normalizados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes Brutos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDC e Normalizados'!$A$1:$E$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Componentes Brutos'!$A$1:$D$185</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +32,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,31 +434,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>C_norm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>I_norm</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Q_norm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
@@ -450,10 +477,10 @@
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -461,10 +488,10 @@
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -472,10 +499,10 @@
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,10 +510,10 @@
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -494,10 +521,10 @@
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -505,10 +532,10 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -516,10 +543,10 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -527,10 +554,10 @@
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -538,10 +565,10 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,10 +576,10 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -560,10 +587,10 @@
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,10 +598,10 @@
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -582,10 +609,10 @@
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -593,10 +620,10 @@
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -604,10 +631,10 @@
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -615,10 +642,10 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -626,10 +653,10 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -637,10 +664,10 @@
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -648,10 +675,10 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -659,10 +686,10 @@
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -670,10 +697,10 @@
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -681,10 +708,10 @@
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -692,10 +719,10 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -703,10 +730,10 @@
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -714,10 +741,10 @@
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -725,10 +752,10 @@
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -736,10 +763,10 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,10 +774,10 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -758,10 +785,10 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -769,10 +796,10 @@
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -780,10 +807,10 @@
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -791,10 +818,10 @@
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -802,10 +829,10 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -813,10 +840,10 @@
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -824,16 +851,16 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="2" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="2" t="n">
         <v>0.2422116758283082</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="2" t="n">
         <v>0.1805589721566735</v>
       </c>
     </row>
@@ -843,16 +870,16 @@
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="2" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="2" t="n">
         <v>0.05882352941176449</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="2" t="n">
         <v>0.8452633369830688</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="2" t="n">
         <v>0.3619683494043387</v>
       </c>
     </row>
@@ -862,16 +889,16 @@
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="2" t="n">
         <v>0.1363636363636367</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="2" t="n">
         <v>0.05882352941176449</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="2" t="n">
         <v>0.3983957219251337</v>
       </c>
     </row>
@@ -881,16 +908,16 @@
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="2" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="2" t="n">
         <v>0.4331550802139041</v>
       </c>
     </row>
@@ -900,16 +927,16 @@
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="2" t="n">
         <v>0.176470588235294</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="2" t="n">
         <v>0.9680561565490443</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="2" t="n">
         <v>0.4572664906856885</v>
       </c>
     </row>
@@ -919,16 +946,16 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="2" t="n">
         <v>0.2727272727272735</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="2" t="n">
         <v>0.4634581105169344</v>
       </c>
     </row>
@@ -938,16 +965,16 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="2" t="n">
         <v>0.2727272727272735</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="2" t="n">
         <v>0.8496519028298313</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="2" t="n">
         <v>0.4133420781268781</v>
       </c>
     </row>
@@ -957,16 +984,16 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="2" t="n">
         <v>0.8545129700067381</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="2" t="n">
         <v>0.3998109187009983</v>
       </c>
     </row>
@@ -976,16 +1003,16 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="2" t="n">
         <v>0.8905612560660224</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="2" t="n">
         <v>0.4118270140540931</v>
       </c>
     </row>
@@ -995,16 +1022,16 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="2" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="2" t="n">
         <v>0.8049778965668238</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="2" t="n">
         <v>0.3832992275543602</v>
       </c>
     </row>
@@ -1014,16 +1041,16 @@
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="2" t="n">
         <v>0.4090909090909102</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="2" t="n">
         <v>0.713339192629582</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="2" t="n">
         <v>0.374143367240164</v>
       </c>
     </row>
@@ -1033,16 +1060,16 @@
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="2" t="n">
         <v>0.5909090909090914</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="2" t="n">
         <v>0.2830795797543156</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="2" t="n">
         <v>0.2913295568878023</v>
       </c>
     </row>
@@ -1052,16 +1079,16 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="2" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="2" t="n">
         <v>0.5088844678235531</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="2" t="n">
         <v>0.4272039135169419</v>
       </c>
     </row>
@@ -1071,16 +1098,16 @@
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="2" t="n">
         <v>0.8636363636363649</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="2" t="n">
         <v>0.7821129659347716</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="2" t="n">
         <v>0.5485831098570455</v>
       </c>
     </row>
@@ -1090,16 +1117,16 @@
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="2" t="n">
         <v>0.8181818181818188</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="2" t="n">
         <v>0.7541968664744032</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="2" t="n">
         <v>0.5241262282187407</v>
       </c>
     </row>
@@ -1109,16 +1136,16 @@
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="2" t="n">
         <v>0.9090909090909094</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="2" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>0.9279450862400527</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="2" t="n">
         <v>0.629011998443654</v>
       </c>
     </row>
@@ -1128,16 +1155,16 @@
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="2" t="n">
         <v>0.9090909090909094</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="2" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="2" t="n">
         <v>0.9427410119443859</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="2" t="n">
         <v>0.6672773070117651</v>
       </c>
     </row>
@@ -1147,16 +1174,16 @@
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="2" t="n">
         <v>0.9545454545454555</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="2" t="n">
         <v>0.1000000000000001</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="2" t="n">
         <v>0.9794445854035727</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="2" t="n">
         <v>0.6779966799830094</v>
       </c>
     </row>
@@ -1166,16 +1193,16 @@
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="2" t="n">
         <v>0.9545454545454555</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="2" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="2" t="n">
         <v>0.9008948618122039</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="2" t="n">
         <v>0.6684801054525531</v>
       </c>
     </row>
@@ -1185,16 +1212,16 @@
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="2" t="n">
         <v>0.9730946232195287</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="2" t="n">
         <v>0.7410315410731761</v>
       </c>
     </row>
@@ -1204,16 +1231,16 @@
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="2" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="2" t="n">
         <v>0.7666666666666666</v>
       </c>
     </row>
@@ -1223,16 +1250,16 @@
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="2" t="n">
         <v>0.8333333333333326</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="2" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="2" t="n">
         <v>0.7111111111111108</v>
       </c>
     </row>
@@ -1242,16 +1269,16 @@
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="2" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="2" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="2" t="n">
         <v>0.9947231748960665</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="2" t="n">
         <v>0.6732410582986886</v>
       </c>
     </row>
@@ -1261,16 +1288,16 @@
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="2" t="n">
         <v>0.6194851476334481</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="2" t="n">
         <v>0.4842728269889271</v>
       </c>
     </row>
@@ -1280,16 +1307,16 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="2" t="n">
         <v>0.4583333333333335</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="2" t="n">
         <v>0.814703135677309</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="2" t="n">
         <v>0.6076788230035475</v>
       </c>
     </row>
@@ -1299,16 +1326,16 @@
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="2" t="n">
         <v>0.4999999999999993</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="2" t="n">
         <v>0.683333333333333</v>
       </c>
     </row>
@@ -1318,16 +1345,16 @@
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="2" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>0.976211959824916</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="2" t="n">
         <v>0.7004039866083053</v>
       </c>
     </row>
@@ -1337,16 +1364,16 @@
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="2" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="2" t="n">
         <v>0.7249999999999998</v>
       </c>
     </row>
@@ -1356,16 +1383,16 @@
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="2" t="n">
         <v>0.7499999999999997</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="2" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="2" t="n">
         <v>0.9766249935913064</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="2" t="n">
         <v>0.7755416645304353</v>
       </c>
     </row>
@@ -1375,16 +1402,16 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="2" t="n">
         <v>0.7499999999999997</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="2" t="n">
         <v>0.9413080276142702</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="2" t="n">
         <v>0.7304360092047566</v>
       </c>
     </row>
@@ -1394,16 +1421,16 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="2" t="n">
         <v>0.8704106420610767</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="2" t="n">
         <v>0.6956924362425809</v>
       </c>
     </row>
@@ -1413,16 +1440,16 @@
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="2" t="n">
         <v>0.8236933452801616</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="2" t="n">
         <v>0.680120003982276</v>
       </c>
     </row>
@@ -1432,16 +1459,16 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="2" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="2" t="n">
         <v>0.8656792718241696</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="2" t="n">
         <v>0.6941153128302786</v>
       </c>
     </row>
@@ -1451,16 +1478,16 @@
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="2" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="2" t="n">
         <v>0.8375821687703922</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="2" t="n">
         <v>0.6541940562567973</v>
       </c>
     </row>
@@ -1470,16 +1497,16 @@
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="2" t="n">
         <v>0.5833333333333337</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="2" t="n">
         <v>0.6917450670248385</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="2" t="n">
         <v>0.5916928001193907</v>
       </c>
     </row>
@@ -1489,16 +1516,16 @@
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="2" t="n">
         <v>0.4166666666666663</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="2" t="n">
         <v>0.4499999999999997</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="2" t="n">
         <v>0.2724702528146602</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="2" t="n">
         <v>0.3797123064937755</v>
       </c>
     </row>
@@ -1508,16 +1535,16 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="2" t="n">
         <v>0.4166666666666663</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="2" t="n">
         <v>0.4499999999999997</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="2" t="n">
         <v>0.4014108069632996</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="2" t="n">
         <v>0.4226924912099885</v>
       </c>
     </row>
@@ -1527,16 +1554,16 @@
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="2" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="2" t="n">
         <v>0.5102113018006617</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="2" t="n">
         <v>0.4145148783779982</v>
       </c>
     </row>
@@ -1546,16 +1573,16 @@
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="2" t="n">
         <v>0.2916666666666661</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="2" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="2" t="n">
         <v>0.424598883606307</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="2" t="n">
         <v>0.3720885167576577</v>
       </c>
     </row>
@@ -1565,16 +1592,16 @@
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="2" t="n">
         <v>0.1250000000000002</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="2" t="n">
         <v>0.3500000000000001</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="2" t="n">
         <v>0.4917212815545563</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="2" t="n">
         <v>0.3222404271848522</v>
       </c>
     </row>
@@ -1584,16 +1611,16 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="2" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="2" t="n">
         <v>0.4561832144991673</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="2" t="n">
         <v>0.2853944048330557</v>
       </c>
     </row>
@@ -1603,16 +1630,16 @@
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="2" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="2" t="n">
         <v>0.3843416404621943</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="2" t="n">
         <v>0.2281138801540647</v>
       </c>
     </row>
@@ -1622,16 +1649,16 @@
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="2" t="n">
         <v>0.04166666666666722</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="2" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="2" t="n">
         <v>0.3187939095792203</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="2" t="n">
         <v>0.2201535254152958</v>
       </c>
     </row>
@@ -1641,16 +1668,16 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="2" t="n">
         <v>0.2083333333333331</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="2" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="2" t="n">
         <v>0.2479810814968522</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="2" t="n">
         <v>0.2521048049433951</v>
       </c>
     </row>
@@ -1660,16 +1687,16 @@
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="2" t="n">
         <v>0.2500000000000004</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="2" t="n">
         <v>0.1974502257562492</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="2" t="n">
         <v>0.2324834085854165</v>
       </c>
     </row>
@@ -1679,16 +1706,16 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="2" t="n">
         <v>0.1666666666666674</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="2" t="n">
         <v>0.1999999999999997</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="2" t="n">
         <v>0.1990704171206821</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="2" t="n">
         <v>0.1885790279291164</v>
       </c>
     </row>
@@ -1698,16 +1725,16 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="2" t="n">
         <v>0.04166666666666722</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="2" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="2" t="n">
         <v>0.09469954379412228</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="2" t="n">
         <v>0.09545540348692981</v>
       </c>
     </row>
@@ -1717,16 +1744,16 @@
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="2" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="2" t="n">
         <v>0.01666666666666661</v>
       </c>
     </row>
@@ -1736,16 +1763,16 @@
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="2" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="2" t="n">
         <v>0.0919668901002043</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="2" t="n">
         <v>0.04732229670006805</v>
       </c>
     </row>
@@ -1755,16 +1782,16 @@
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="2" t="n">
         <v>0.2606429582478396</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="2" t="n">
         <v>0.08688098608261319</v>
       </c>
     </row>
@@ -1774,16 +1801,16 @@
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="2" t="n">
         <v>0.03703703703703753</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>0.1986749147155459</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="2" t="n">
         <v>0.07857065058419449</v>
       </c>
     </row>
@@ -1793,16 +1820,16 @@
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="2" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="2" t="n">
         <v>0.2344603022598383</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="2" t="n">
         <v>0.1151904711236498</v>
       </c>
     </row>
@@ -1812,16 +1839,16 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="2" t="n">
         <v>0.2222222222222225</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="2" t="n">
         <v>0.1789173120196445</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="2" t="n">
         <v>0.1337131780806223</v>
       </c>
     </row>
@@ -1831,16 +1858,16 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="2" t="n">
         <v>0.37037037037037</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="2" t="n">
         <v>0.2052644274097824</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="2" t="n">
         <v>0.1918782659267174</v>
       </c>
     </row>
@@ -1850,16 +1877,16 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="2" t="n">
         <v>0.185185185185185</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="2" t="n">
         <v>0.04545454545454529</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="2" t="n">
         <v>0.1213751722158816</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="2" t="n">
         <v>0.1173383009518706</v>
       </c>
     </row>
@@ -1869,16 +1896,16 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="2" t="n">
         <v>0.07407407407407506</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="2" t="n">
         <v>0.04545454545454529</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="2" t="n">
         <v>0.06988382567382279</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="2" t="n">
         <v>0.06313748173414771</v>
       </c>
     </row>
@@ -1888,16 +1915,16 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="2" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="2" t="n">
         <v>0.05070704636073997</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="2" t="n">
         <v>0.05393938582395041</v>
       </c>
     </row>
@@ -1907,16 +1934,16 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="2" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="2" t="n">
         <v>0.08470716949469945</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="2" t="n">
         <v>0.0652727602019369</v>
       </c>
     </row>
@@ -1926,16 +1953,16 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="2" t="n">
         <v>0.1481481481481488</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="2" t="n">
         <v>0.01775627016430798</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="2" t="n">
         <v>0.05530147277081892</v>
       </c>
     </row>
@@ -1945,16 +1972,16 @@
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="2" t="n">
         <v>0.25925925925926</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="2" t="n">
         <v>0.08641975308642001</v>
       </c>
     </row>
@@ -1964,16 +1991,16 @@
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="2" t="n">
         <v>0.3333333333333338</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="2" t="n">
         <v>0.1274114744239928</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="2" t="n">
         <v>0.1535816025857755</v>
       </c>
     </row>
@@ -1983,16 +2010,16 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="2" t="n">
         <v>0.4074074074074075</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="2" t="n">
         <v>0.251827182758644</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="2" t="n">
         <v>0.2197448633886838</v>
       </c>
     </row>
@@ -2002,16 +2029,16 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="2" t="n">
         <v>0.4074074074074075</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="2" t="n">
         <v>0.2403322312375094</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="2" t="n">
         <v>0.215913212881639</v>
       </c>
     </row>
@@ -2021,16 +2048,16 @@
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="2" t="n">
         <v>0.5925925925925924</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="2" t="n">
         <v>0.2958785670844841</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="2" t="n">
         <v>0.2961570532256922</v>
       </c>
     </row>
@@ -2040,16 +2067,16 @@
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="2" t="n">
         <v>0.7407407407407399</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="2" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="2" t="n">
         <v>0.3019317271839393</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="2" t="n">
         <v>0.3614463781971153</v>
       </c>
     </row>
@@ -2059,16 +2086,16 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="2" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="2" t="n">
         <v>0.3650606198010092</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="2" t="n">
         <v>0.4689090954892254</v>
       </c>
     </row>
@@ -2078,16 +2105,16 @@
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="2" t="n">
         <v>0.8749999999999994</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="2" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="2" t="n">
         <v>0.2989804724093655</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="2" t="n">
         <v>0.4052157130253439</v>
       </c>
     </row>
@@ -2097,16 +2124,16 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="2" t="n">
         <v>0.8749999999999994</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="2" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="2" t="n">
         <v>0.2942301618472238</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="2" t="n">
         <v>0.4036322761712967</v>
       </c>
     </row>
@@ -2116,16 +2143,16 @@
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="2" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="2" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="2" t="n">
         <v>0.2955600487797549</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="2" t="n">
         <v>0.3485200162599181</v>
       </c>
     </row>
@@ -2135,16 +2162,16 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="2" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="2" t="n">
         <v>0.2544007488826512</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="2" t="n">
         <v>0.2931335829608837</v>
       </c>
     </row>
@@ -2154,16 +2181,16 @@
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="2" t="n">
         <v>0.3437500000000001</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="2" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="2" t="n">
         <v>0.210876468714607</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="2" t="n">
         <v>0.2265421562382023</v>
       </c>
     </row>
@@ -2173,16 +2200,16 @@
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="2" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="2" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="2" t="n">
         <v>0.03320867850220396</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="2" t="n">
         <v>0.1256528928340682</v>
       </c>
     </row>
@@ -2192,16 +2219,16 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="2" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="2" t="n">
         <v>0.0833333333333334</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="2" t="n">
         <v>0.1143472688322961</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="2" t="n">
         <v>0.1388102007218767</v>
       </c>
     </row>
@@ -2211,16 +2238,16 @@
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="2" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="2" t="n">
         <v>0.1666666666666668</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="2" t="n">
         <v>0.2186032841721531</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="2" t="n">
         <v>0.2013399836129402</v>
       </c>
     </row>
@@ -2230,16 +2257,16 @@
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="2" t="n">
         <v>0.5624999999999998</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="2" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="2" t="n">
         <v>0.2608852353232828</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="2" t="n">
         <v>0.3439061895522053</v>
       </c>
     </row>
@@ -2249,16 +2276,16 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="2" t="n">
         <v>0.4062499999999999</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="2" t="n">
         <v>0.3333333333333332</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="2" t="n">
         <v>0.4496545779210505</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="2" t="n">
         <v>0.3964126370847945</v>
       </c>
     </row>
@@ -2268,16 +2295,16 @@
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="2" t="n">
         <v>0.3750000000000001</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="2" t="n">
         <v>0.3358003984846665</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="2" t="n">
         <v>0.2369334661615556</v>
       </c>
     </row>
@@ -2287,16 +2314,16 @@
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="2" t="n">
         <v>0.2500000000000002</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="2" t="n">
         <v>0.1839690628946757</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="2" t="n">
         <v>0.1446563542982253</v>
       </c>
     </row>
@@ -2306,16 +2333,16 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="2" t="n">
         <v>0.1666666666666668</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="2" t="n">
         <v>0.02988643543015799</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="2" t="n">
         <v>0.0655177006989416</v>
       </c>
     </row>
@@ -2325,16 +2352,16 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="2" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="2" t="n">
         <v>0.01388888888888896</v>
       </c>
     </row>
@@ -2344,16 +2371,16 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="2" t="n">
         <v>0.03773584905660363</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="2" t="n">
         <v>0.01257861635220121</v>
       </c>
     </row>
@@ -2363,16 +2390,16 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="2" t="n">
         <v>0.1320754716981131</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="2" t="n">
         <v>0.04402515723270436</v>
       </c>
     </row>
@@ -2382,16 +2409,16 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="2" t="n">
         <v>0.2830188679245282</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="2" t="n">
         <v>0.09433962264150941</v>
       </c>
     </row>
@@ -2401,16 +2428,16 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="2" t="n">
         <v>0.3773584905660377</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="2" t="n">
         <v>0.1257861635220126</v>
       </c>
     </row>
@@ -2420,16 +2447,16 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="2" t="n">
         <v>0.452830188679245</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="2" t="n">
         <v>0.08432386816264849</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="2" t="n">
         <v>0.1790513522806312</v>
       </c>
     </row>
@@ -2439,16 +2466,16 @@
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="2" t="n">
         <v>0.4150943396226413</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="2" t="n">
         <v>0.1797646780629271</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="2" t="n">
         <v>0.1982863392285228</v>
       </c>
     </row>
@@ -2458,16 +2485,16 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="2" t="n">
         <v>0.4716981132075471</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="2" t="n">
         <v>0.222881401686199</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="2" t="n">
         <v>0.231526504964582</v>
       </c>
     </row>
@@ -2477,16 +2504,16 @@
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="2" t="n">
         <v>0.4905660377358486</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="2" t="n">
         <v>0.2578785365837941</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="2" t="n">
         <v>0.2494815247732142</v>
       </c>
     </row>
@@ -2496,16 +2523,16 @@
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="2" t="n">
         <v>0.5660377358490565</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="2" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="2" t="n">
         <v>0.2621361910098082</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="2" t="n">
         <v>0.2868106637916646</v>
       </c>
     </row>
@@ -2515,16 +2542,16 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="2" t="n">
         <v>0.6037735849056601</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="2" t="n">
         <v>0.2912782721622858</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="2" t="n">
         <v>0.2983506190226486</v>
       </c>
     </row>
@@ -2534,16 +2561,16 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="2" t="n">
         <v>0.660377358490566</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="2" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="2" t="n">
         <v>0.3010636222012054</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="2" t="n">
         <v>0.3312330150693002</v>
       </c>
     </row>
@@ -2553,16 +2580,16 @@
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="2" t="n">
         <v>0.7169811320754718</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="2" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="2" t="n">
         <v>0.3704465919714397</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="2" t="n">
         <v>0.3732285961876802</v>
       </c>
     </row>
@@ -2572,16 +2599,16 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="2" t="n">
         <v>0.8867924528301884</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="2" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="2" t="n">
         <v>0.4501251535328989</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="2" t="n">
         <v>0.4671445784651151</v>
       </c>
     </row>
@@ -2591,16 +2618,16 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="2" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="2" t="n">
         <v>0.529685447230225</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="2" t="n">
         <v>0.5314005254208277</v>
       </c>
     </row>
@@ -2610,16 +2637,16 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="2" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="2" t="n">
         <v>0.5410085340371137</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="2" t="n">
         <v>0.5351748876897906</v>
       </c>
     </row>
@@ -2629,16 +2656,16 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="2" t="n">
         <v>0.09677419354838732</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="2" t="n">
         <v>0.5304280387025574</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="2" t="n">
         <v>0.5424007440836482</v>
       </c>
     </row>
@@ -2648,16 +2675,16 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="2" t="n">
         <v>0.1935483870967743</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="2" t="n">
         <v>0.712021342487658</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="2" t="n">
         <v>0.6351899098614774</v>
       </c>
     </row>
@@ -2667,16 +2694,16 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="2" t="n">
         <v>0.9354838709677421</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="2" t="n">
         <v>0.2258064516129032</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="2" t="n">
         <v>0.8232897008055995</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="2" t="n">
         <v>0.6615266744620817</v>
       </c>
     </row>
@@ -2686,16 +2713,16 @@
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="2" t="n">
         <v>0.9032258064516127</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="2" t="n">
         <v>0.2580645161290324</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="2" t="n">
         <v>0.8324649346273065</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="2" t="n">
         <v>0.6645850857359838</v>
       </c>
     </row>
@@ -2705,16 +2732,16 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="2" t="n">
         <v>0.9354838709677421</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="2" t="n">
         <v>0.3225806451612903</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="2" t="n">
         <v>0.8567918560870487</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="2" t="n">
         <v>0.704952124072027</v>
       </c>
     </row>
@@ -2724,16 +2751,16 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="2" t="n">
         <v>0.9032258064516127</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="2" t="n">
         <v>0.4193548387096776</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="2" t="n">
         <v>0.8694618519767494</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="2" t="n">
         <v>0.7306808323793467</v>
       </c>
     </row>
@@ -2743,16 +2770,16 @@
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="2" t="n">
         <v>0.3870967741935484</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="2" t="n">
         <v>0.89261006526663</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="2" t="n">
         <v>0.7599022798200595</v>
       </c>
     </row>
@@ -2762,16 +2789,16 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="2" t="n">
         <v>0.9081061978823698</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="2" t="n">
         <v>0.7973257218747684</v>
       </c>
     </row>
@@ -2781,16 +2808,16 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="2" t="n">
         <v>0.9115653228019891</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="2" t="n">
         <v>0.8092314516866845</v>
       </c>
     </row>
@@ -2800,16 +2827,16 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="2" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="2" t="n">
         <v>0.9618217250861214</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="2" t="n">
         <v>0.8367362739534383</v>
       </c>
     </row>
@@ -2819,16 +2846,16 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="2" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="2" t="n">
         <v>0.9760134220462652</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="2" t="n">
         <v>0.8522195277788627</v>
       </c>
     </row>
@@ -2838,16 +2865,16 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="2" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="2" t="n">
         <v>0.9663459569184722</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="2" t="n">
         <v>0.8489970394029317</v>
       </c>
     </row>
@@ -2857,16 +2884,16 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="2" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="2" t="n">
         <v>0.9118676661595573</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="2" t="n">
         <v>0.841590297322003</v>
       </c>
     </row>
@@ -2876,16 +2903,16 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="2" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="2" t="n">
         <v>0.9645308291811198</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="2" t="n">
         <v>0.8806500613399432</v>
       </c>
     </row>
@@ -2895,16 +2922,16 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="2" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="2" t="n">
         <v>0.89247311827957</v>
       </c>
     </row>
@@ -2914,16 +2941,16 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="2" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="2" t="n">
         <v>0.9536012688232502</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="2" t="n">
         <v>0.8770068745539866</v>
       </c>
     </row>
@@ -2933,16 +2960,16 @@
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="2" t="n">
         <v>0.7096774193548386</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="2" t="n">
         <v>0.9032258064516129</v>
       </c>
     </row>
@@ -2952,16 +2979,16 @@
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="2" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="2" t="n">
         <v>0.9870362672921551</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="2" t="n">
         <v>0.9204099385597506</v>
       </c>
     </row>
@@ -2971,16 +2998,16 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="2" t="n">
         <v>0.9756097560975611</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="2" t="n">
         <v>0.7419354838709679</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="2" t="n">
         <v>0.9400328488618431</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="2" t="n">
         <v>0.8858593629434574</v>
       </c>
     </row>
@@ -2990,16 +3017,16 @@
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="2" t="n">
         <v>0.9146341463414634</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="2" t="n">
         <v>0.7096774193548386</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="2" t="n">
         <v>0.8992342954046627</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="2" t="n">
         <v>0.8411819537003216</v>
       </c>
     </row>
@@ -3009,16 +3036,16 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="2" t="n">
         <v>0.8658536585365851</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="2" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="2" t="n">
         <v>0.905661888760471</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="2" t="n">
         <v>0.8163116340452552</v>
       </c>
     </row>
@@ -3028,16 +3055,16 @@
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="2" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="2" t="n">
         <v>0.6451612903225805</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="2" t="n">
         <v>0.8676545073159999</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="2" t="n">
         <v>0.7888247780746488</v>
       </c>
     </row>
@@ -3047,16 +3074,16 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="2" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="2" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="2" t="n">
         <v>0.8776942275584794</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="2" t="n">
         <v>0.7814186633167658</v>
       </c>
     </row>
@@ -3066,16 +3093,16 @@
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="2" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="2" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="2" t="n">
         <v>0.8610748614383315</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="2" t="n">
         <v>0.7529310644867871</v>
       </c>
     </row>
@@ -3085,16 +3112,16 @@
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="2" t="n">
         <v>0.7317073170731708</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="2" t="n">
         <v>0.7649517439682593</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="2" t="n">
         <v>0.670929364433165</v>
       </c>
     </row>
@@ -3104,16 +3131,16 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" s="2" t="n">
         <v>0.7195121951219511</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="2" t="n">
         <v>0.8546303861228126</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="2" t="n">
         <v>0.6967572045009428</v>
       </c>
     </row>
@@ -3123,16 +3150,16 @@
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="2" t="n">
         <v>0.7317073170731708</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="2" t="n">
         <v>0.9286928511987693</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="2" t="n">
         <v>0.7255097335100015</v>
       </c>
     </row>
@@ -3142,16 +3169,16 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="2" t="n">
         <v>0.7682926829268294</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="2" t="n">
         <v>0.9308507343731816</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="2" t="n">
         <v>0.7276714616806488</v>
       </c>
     </row>
@@ -3161,16 +3188,16 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="2" t="n">
         <v>0.7682926829268294</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="2" t="n">
         <v>0.9394464189797158</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="2" t="n">
         <v>0.7305366898828268</v>
       </c>
     </row>
@@ -3180,16 +3207,16 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="2" t="n">
         <v>0.7560975609756098</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="2" t="n">
         <v>0.9253709050813183</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="2" t="n">
         <v>0.732532499438331</v>
       </c>
     </row>
@@ -3199,16 +3226,16 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="2" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="2" t="n">
         <v>0.9033261872580214</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="2" t="n">
         <v>0.7306917345934815</v>
       </c>
     </row>
@@ -3218,16 +3245,16 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="2" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="2" t="n">
         <v>0.8878202834579203</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="2" t="n">
         <v>0.7295881406438544</v>
       </c>
     </row>
@@ -3237,16 +3264,16 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="2" t="n">
         <v>0.8414634146341462</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="2" t="n">
         <v>0.9089182446586339</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="2" t="n">
         <v>0.7555035638502815</v>
       </c>
     </row>
@@ -3256,16 +3283,16 @@
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" s="2" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="2" t="n">
         <v>0.950550637770796</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="2" t="n">
         <v>0.7612509469201892</v>
       </c>
     </row>
@@ -3275,16 +3302,16 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="2" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="2" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="2" t="n">
         <v>0.9523360219468819</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="2" t="n">
         <v>0.747028346156435</v>
       </c>
     </row>
@@ -3294,16 +3321,16 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="2" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="2" t="n">
         <v>0.4516129032258065</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="2" t="n">
         <v>0.9270210444649277</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="2" t="n">
         <v>0.7278373321570739</v>
       </c>
     </row>
@@ -3313,16 +3340,16 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="2" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="2" t="n">
         <v>0.4193548387096776</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="2" t="n">
         <v>0.8770978510901344</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="2" t="n">
         <v>0.7167037421283927</v>
       </c>
     </row>
@@ -3332,16 +3359,16 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="2" t="n">
         <v>0.8414634146341462</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="2" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="2" t="n">
         <v>0.9835733002093877</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" s="2" t="n">
         <v>0.7803885823671995</v>
       </c>
     </row>
@@ -3351,16 +3378,16 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="2" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="2" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="2" t="n">
         <v>0.8006818777865199</v>
       </c>
     </row>
@@ -3370,16 +3397,16 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="2" t="n">
         <v>0.8780487804878049</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="2" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="2" t="n">
         <v>0.8195646472593759</v>
       </c>
     </row>
@@ -3389,16 +3416,16 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="2" t="n">
         <v>0.8902439024390245</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="2" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="2" t="n">
         <v>0.8558877524259114</v>
       </c>
     </row>
@@ -3408,16 +3435,16 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" s="2" t="n">
         <v>0.9024390243902438</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="2" t="n">
         <v>0.7419354838709679</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="2" t="n">
         <v>0.8814581694204039</v>
       </c>
     </row>
@@ -3427,16 +3454,16 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="2" t="n">
         <v>0.9024390243902438</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="2" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="2" t="n">
         <v>0.8922108575924469</v>
       </c>
     </row>
@@ -3446,16 +3473,16 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" s="2" t="n">
         <v>0.9146341463414634</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="2" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="2" t="n">
         <v>0.994697007603812</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="2" t="n">
         <v>0.9160136104548767</v>
       </c>
     </row>
@@ -3465,16 +3492,16 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="2" t="n">
         <v>0.9512195121951221</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="2" t="n">
         <v>0.9354838709677419</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="2" t="n">
         <v>0.962234461054288</v>
       </c>
     </row>
@@ -3484,16 +3511,16 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="2" t="n">
         <v>0.9756097560975611</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="2" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="2" t="n">
         <v>0.9596118541830579</v>
       </c>
     </row>
@@ -3503,16 +3530,16 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="2" t="n">
         <v>0.9878048780487804</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="2" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="2" t="n">
         <v>0.9636768948334645</v>
       </c>
     </row>
@@ -3522,17 +3549,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="2" t="n">
         <v>0.9878048780487804</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="2" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D178" t="n">
-        <v>0.9926387329695173</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.9612231391566369</v>
+      <c r="D178" s="2" t="n">
+        <v>0.9922483704090016</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>0.9610930183031318</v>
       </c>
     </row>
     <row r="179">
@@ -3541,17 +3568,17 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="2" t="n">
         <v>0.9677419354838708</v>
       </c>
-      <c r="D179" t="n">
-        <v>0.9207868286683762</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.9628429213840825</v>
+      <c r="D179" s="2" t="n">
+        <v>0.920472930072725</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>0.9627382885188652</v>
       </c>
     </row>
     <row r="180">
@@ -3560,17 +3587,17 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D180" t="n">
-        <v>0.9879257613712907</v>
-      </c>
-      <c r="E180" t="n">
-        <v>0.9959752537904302</v>
+      <c r="D180" s="2" t="n">
+        <v>0.9877814324465222</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>0.9959271441488408</v>
       </c>
     </row>
     <row r="181">
@@ -3579,16 +3606,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3598,17 +3625,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="2" t="n">
         <v>0.9882352941176469</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="2" t="n">
         <v>0.9393939393939393</v>
       </c>
-      <c r="D182" t="n">
-        <v>0.9532678679451505</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0.9602990338189121</v>
+      <c r="D182" s="2" t="n">
+        <v>0.9534840917507833</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>0.9603711084207899</v>
       </c>
     </row>
     <row r="183">
@@ -3617,17 +3644,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D183" t="n">
-        <v>0.9710636030967117</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0.9903545343655705</v>
+      <c r="D183" s="2" t="n">
+        <v>0.9712941575502504</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>0.9904313858500835</v>
       </c>
     </row>
     <row r="184">
@@ -3636,20 +3663,40 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D184" t="n">
-        <v>0.9436946533708811</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0.981231551123627</v>
+      <c r="D184" s="2" t="n">
+        <v>0.9496989605019228</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>0.9832329868339743</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>0.9705882352941178</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0.9070197678750417</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>0.9592026677230532</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3660,26 +3707,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
@@ -3691,13 +3744,13 @@
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.2144837064952339</v>
       </c>
     </row>
@@ -3707,13 +3760,13 @@
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0.216318931938421</v>
       </c>
     </row>
@@ -3723,13 +3776,13 @@
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>0.2155671126202916</v>
       </c>
     </row>
@@ -3739,13 +3792,13 @@
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0.2158826655184728</v>
       </c>
     </row>
@@ -3755,13 +3808,13 @@
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>0.2133800314704837</v>
       </c>
     </row>
@@ -3771,13 +3824,13 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>0.2142054660256966</v>
       </c>
     </row>
@@ -3787,13 +3840,13 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>0.2163096789499437</v>
       </c>
     </row>
@@ -3803,13 +3856,13 @@
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>0.2179910005812397</v>
       </c>
     </row>
@@ -3819,13 +3872,13 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2" t="n">
         <v>0.2182622171978539</v>
       </c>
     </row>
@@ -3835,13 +3888,13 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2" t="n">
         <v>0.2133141087974606</v>
       </c>
     </row>
@@ -3851,13 +3904,13 @@
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>0.21806653595598</v>
       </c>
     </row>
@@ -3867,13 +3920,13 @@
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>0.2219530188435359</v>
       </c>
     </row>
@@ -3883,13 +3936,13 @@
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="2" t="n">
         <v>0.2215058239527761</v>
       </c>
     </row>
@@ -3899,13 +3952,13 @@
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="2" t="n">
         <v>0.2221233325942454</v>
       </c>
     </row>
@@ -3915,13 +3968,13 @@
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2" t="n">
         <v>0.220769753883536</v>
       </c>
     </row>
@@ -3931,13 +3984,13 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>0.2197200510871163</v>
       </c>
     </row>
@@ -3947,13 +4000,13 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>0.2177195914744852</v>
       </c>
     </row>
@@ -3963,13 +4016,13 @@
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="2" t="n">
         <v>0.2163159091483287</v>
       </c>
     </row>
@@ -3979,13 +4032,13 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="2" t="n">
         <v>0.2204091315317143</v>
       </c>
     </row>
@@ -3995,13 +4048,13 @@
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="2" t="n">
         <v>0.2193257789363551</v>
       </c>
     </row>
@@ -4011,13 +4064,13 @@
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>0.2184516937304613</v>
       </c>
     </row>
@@ -4027,13 +4080,13 @@
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="2" t="n">
         <v>0.2113327832216916</v>
       </c>
     </row>
@@ -4043,13 +4096,13 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="2" t="n">
         <v>0.2105058800605199</v>
       </c>
     </row>
@@ -4059,13 +4112,13 @@
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="2" t="n">
         <v>0.2146924625203246</v>
       </c>
     </row>
@@ -4075,13 +4128,13 @@
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2" t="n">
         <v>0.214597665058659</v>
       </c>
     </row>
@@ -4091,13 +4144,13 @@
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="2" t="n">
         <v>0.215024108630904</v>
       </c>
     </row>
@@ -4107,13 +4160,13 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="2" t="n">
         <v>0.2136504283411237</v>
       </c>
     </row>
@@ -4123,13 +4176,13 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="2" t="n">
         <v>0.2142377228564658</v>
       </c>
     </row>
@@ -4139,13 +4192,13 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="2" t="n">
         <v>0.2123923622042895</v>
       </c>
     </row>
@@ -4155,13 +4208,13 @@
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="2" t="n">
         <v>0.2130640498279781</v>
       </c>
     </row>
@@ -4171,13 +4224,13 @@
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="2" t="n">
         <v>0.2161353832177457</v>
       </c>
     </row>
@@ -4187,13 +4240,13 @@
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="2" t="n">
         <v>0.21538183222886</v>
       </c>
     </row>
@@ -4203,13 +4256,13 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="2" t="n">
         <v>0.2149883683635729</v>
       </c>
     </row>
@@ -4219,13 +4272,13 @@
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="2" t="n">
         <v>0.2094029707921079</v>
       </c>
     </row>
@@ -4235,13 +4288,13 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="2" t="n">
         <v>0.212483990941346</v>
       </c>
     </row>
@@ -4251,13 +4304,13 @@
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="2" t="n">
         <v>0.2201550262566146</v>
       </c>
     </row>
@@ -4267,13 +4320,13 @@
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="2" t="n">
         <v>0.2223286212692439</v>
       </c>
     </row>
@@ -4283,13 +4336,13 @@
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="2" t="n">
         <v>0.2252691174230988</v>
       </c>
     </row>
@@ -4299,13 +4352,13 @@
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="2" t="n">
         <v>0.2247622917189485</v>
       </c>
     </row>
@@ -4315,13 +4368,13 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="2" t="n">
         <v>0.2272836840920228</v>
       </c>
     </row>
@@ -4331,13 +4384,13 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="2" t="n">
         <v>0.2245953528713353</v>
       </c>
     </row>
@@ -4347,13 +4400,13 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="2" t="n">
         <v>0.2246822722198572</v>
       </c>
     </row>
@@ -4363,13 +4416,13 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="2" t="n">
         <v>0.2253268412878366</v>
       </c>
     </row>
@@ -4379,13 +4432,13 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="2" t="n">
         <v>0.2237965497733879</v>
       </c>
     </row>
@@ -4395,13 +4448,13 @@
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="2" t="n">
         <v>0.2221579843811103</v>
       </c>
     </row>
@@ -4411,13 +4464,13 @@
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="2" t="n">
         <v>0.2144646355987552</v>
       </c>
     </row>
@@ -4427,13 +4480,13 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="2" t="n">
         <v>0.2185021880640406</v>
       </c>
     </row>
@@ -4443,13 +4496,13 @@
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="2" t="n">
         <v>0.2233877085041337</v>
       </c>
     </row>
@@ -4459,13 +4512,13 @@
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="2" t="n">
         <v>0.2228885487332309</v>
       </c>
     </row>
@@ -4475,13 +4528,13 @@
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>0.2259952908372311</v>
       </c>
     </row>
@@ -4491,13 +4544,13 @@
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="2" t="n">
         <v>0.2262598525427572</v>
       </c>
     </row>
@@ -4507,13 +4560,13 @@
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="2" t="n">
         <v>0.2269161386168632</v>
       </c>
     </row>
@@ -4523,13 +4576,13 @@
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="2" t="n">
         <v>0.2255116135295384</v>
       </c>
     </row>
@@ -4539,13 +4592,13 @@
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="2" t="n">
         <v>0.2268025967635851</v>
       </c>
     </row>
@@ -4555,13 +4608,13 @@
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="2" t="n">
         <v>0.2277693945106953</v>
       </c>
     </row>
@@ -4571,13 +4624,13 @@
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="2" t="n">
         <v>0.2285807873414926</v>
       </c>
     </row>
@@ -4587,13 +4640,13 @@
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="2" t="n">
         <v>0.2284795893576861</v>
       </c>
     </row>
@@ -4603,13 +4656,13 @@
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="2" t="n">
         <v>0.2212833433084906</v>
       </c>
     </row>
@@ -4619,13 +4672,13 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="2" t="n">
         <v>0.2250271980703358</v>
       </c>
     </row>
@@ -4635,13 +4688,13 @@
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="2" t="n">
         <v>0.2290960142036387</v>
       </c>
     </row>
@@ -4651,13 +4704,13 @@
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>0.2286275552957955</v>
       </c>
     </row>
@@ -4667,13 +4720,13 @@
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="2" t="n">
         <v>0.2313727950217048</v>
       </c>
     </row>
@@ -4683,13 +4736,13 @@
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="2" t="n">
         <v>0.2308592502395401</v>
       </c>
     </row>
@@ -4699,13 +4752,13 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="2" t="n">
         <v>0.2300833427047019</v>
       </c>
     </row>
@@ -4715,13 +4768,13 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="2" t="n">
         <v>0.2285257396057603</v>
       </c>
     </row>
@@ -4731,13 +4784,13 @@
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="2" t="n">
         <v>0.2274993688070017</v>
       </c>
     </row>
@@ -4747,13 +4800,13 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="2" t="n">
         <v>0.2284217922332903</v>
       </c>
     </row>
@@ -4763,13 +4816,13 @@
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="2" t="n">
         <v>0.227804503817838</v>
       </c>
     </row>
@@ -4779,13 +4832,13 @@
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="2" t="n">
         <v>0.2246004883263343</v>
       </c>
     </row>
@@ -4795,13 +4848,13 @@
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="2" t="n">
         <v>0.2153890943542398</v>
       </c>
     </row>
@@ -4811,13 +4864,13 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="2" t="n">
         <v>0.2182218956649522</v>
       </c>
     </row>
@@ -4827,13 +4880,13 @@
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="2" t="n">
         <v>0.2206122234126222</v>
       </c>
     </row>
@@ -4843,13 +4896,13 @@
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="2" t="n">
         <v>0.2187313336330215</v>
       </c>
     </row>
@@ -4859,13 +4912,13 @@
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="2" t="n">
         <v>0.2202060009178136</v>
       </c>
     </row>
@@ -4875,13 +4928,13 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="2" t="n">
         <v>0.2194252358311471</v>
       </c>
     </row>
@@ -4891,13 +4944,13 @@
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="2" t="n">
         <v>0.2178468890771772</v>
       </c>
     </row>
@@ -4907,13 +4960,13 @@
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="2" t="n">
         <v>0.2164068169510294</v>
       </c>
     </row>
@@ -4923,13 +4976,13 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="2" t="n">
         <v>0.2148510715648591</v>
       </c>
     </row>
@@ -4939,13 +4992,13 @@
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="2" t="n">
         <v>0.2137409175460669</v>
       </c>
     </row>
@@ -4955,13 +5008,13 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="2" t="n">
         <v>0.2137765128655618</v>
       </c>
     </row>
@@ -4971,13 +5024,13 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="2" t="n">
         <v>0.2114835031238878</v>
       </c>
     </row>
@@ -4987,13 +5040,13 @@
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="2" t="n">
         <v>0.2030377503203539</v>
       </c>
     </row>
@@ -5003,13 +5056,13 @@
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="2" t="n">
         <v>0.2056436362623874</v>
       </c>
     </row>
@@ -5019,13 +5072,13 @@
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="2" t="n">
         <v>0.2104230801933988</v>
       </c>
     </row>
@@ -5035,13 +5088,13 @@
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>0.208667212909856</v>
       </c>
     </row>
@@ -5051,13 +5104,13 @@
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="2" t="n">
         <v>0.2096811934655787</v>
       </c>
     </row>
@@ -5067,13 +5120,13 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="2" t="n">
         <v>0.2081073803542761</v>
       </c>
     </row>
@@ -5083,13 +5136,13 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="2" t="n">
         <v>0.2088539270466073</v>
       </c>
     </row>
@@ -5099,13 +5152,13 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="2" t="n">
         <v>0.2064769212507251</v>
       </c>
     </row>
@@ -5115,13 +5168,13 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="2" t="n">
         <v>0.2050179116447231</v>
       </c>
     </row>
@@ -5131,13 +5184,13 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="2" t="n">
         <v>0.204474536745659</v>
       </c>
     </row>
@@ -5147,13 +5200,13 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="2" t="n">
         <v>0.2054379317545111</v>
       </c>
     </row>
@@ -5163,13 +5216,13 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="2" t="n">
         <v>0.2035408750291889</v>
       </c>
     </row>
@@ -5179,13 +5232,13 @@
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="2" t="n">
         <v>0.1987779985246286</v>
       </c>
     </row>
@@ -5195,13 +5248,13 @@
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="2" t="n">
         <v>0.2029309496048711</v>
       </c>
     </row>
@@ -5211,13 +5264,13 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="2" t="n">
         <v>0.2069862542990786</v>
       </c>
     </row>
@@ -5227,13 +5280,13 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="2" t="n">
         <v>0.2066115786935035</v>
       </c>
     </row>
@@ -5243,13 +5296,13 @@
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="2" t="n">
         <v>0.2084221002065939</v>
       </c>
     </row>
@@ -5259,13 +5312,13 @@
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="2" t="n">
         <v>0.2086194017281998</v>
       </c>
     </row>
@@ -5275,13 +5328,13 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="2" t="n">
         <v>0.210677075136139</v>
       </c>
     </row>
@@ -5291,13 +5344,13 @@
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="2" t="n">
         <v>0.2085232061794116</v>
       </c>
     </row>
@@ -5307,13 +5360,13 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="2" t="n">
         <v>0.2083683707733407</v>
       </c>
     </row>
@@ -5323,13 +5376,13 @@
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="2" t="n">
         <v>0.2084117181672706</v>
       </c>
     </row>
@@ -5339,13 +5392,13 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="2" t="n">
         <v>0.2070701391631624</v>
       </c>
     </row>
@@ -5355,13 +5408,13 @@
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="2" t="n">
         <v>0.2056514741084033</v>
       </c>
     </row>
@@ -5371,13 +5424,13 @@
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="2" t="n">
         <v>0.1998604286423448</v>
       </c>
     </row>
@@ -5387,13 +5440,13 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="2" t="n">
         <v>0.2025051244822138</v>
       </c>
     </row>
@@ -5403,13 +5456,13 @@
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="2" t="n">
         <v>0.2059033280858125</v>
       </c>
     </row>
@@ -5419,13 +5472,13 @@
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="2" t="n">
         <v>0.2072814996790829</v>
       </c>
     </row>
@@ -5435,13 +5488,13 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="2" t="n">
         <v>0.2134343979859439</v>
       </c>
     </row>
@@ -5451,13 +5504,13 @@
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="2" t="n">
         <v>0.2097233441768734</v>
       </c>
     </row>
@@ -5467,13 +5520,13 @@
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="2" t="n">
         <v>0.2047744326914384</v>
       </c>
     </row>
@@ -5483,13 +5536,13 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="2" t="n">
         <v>0.1997521408054976</v>
       </c>
     </row>
@@ -5499,13 +5552,13 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="2" t="n">
         <v>0.195092288385341</v>
       </c>
     </row>
@@ -5515,13 +5568,13 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="2" t="n">
         <v>0.1926571603789215</v>
       </c>
     </row>
@@ -5531,13 +5584,13 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="2" t="n">
         <v>0.1912005200489418</v>
       </c>
     </row>
@@ -5547,13 +5600,13 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="2" t="n">
         <v>0.1865992586106102</v>
       </c>
     </row>
@@ -5563,13 +5616,13 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="2" t="n">
         <v>0.1831479712166515</v>
       </c>
     </row>
@@ -5579,13 +5632,13 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="2" t="n">
         <v>0.1872144749013558</v>
       </c>
     </row>
@@ -5595,13 +5648,13 @@
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="2" t="n">
         <v>0.1918170911426083</v>
       </c>
     </row>
@@ -5611,13 +5664,13 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="2" t="n">
         <v>0.1938963875423917</v>
       </c>
     </row>
@@ -5627,13 +5680,13 @@
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="2" t="n">
         <v>0.1955841182065099</v>
       </c>
     </row>
@@ -5643,13 +5696,13 @@
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="2" t="n">
         <v>0.1957894428410273</v>
       </c>
     </row>
@@ -5659,13 +5712,13 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="2" t="n">
         <v>0.1971948145699181</v>
       </c>
     </row>
@@ -5675,13 +5728,13 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="2" t="n">
         <v>0.1976667113514158</v>
       </c>
     </row>
@@ -5691,13 +5744,13 @@
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="2" t="n">
         <v>0.2010126928436566</v>
       </c>
     </row>
@@ -5707,13 +5760,13 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="2" t="n">
         <v>0.2048551774359981</v>
       </c>
     </row>
@@ -5723,13 +5776,13 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="2" t="n">
         <v>0.2086919585814299</v>
       </c>
     </row>
@@ -5739,13 +5792,13 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="2" t="n">
         <v>0.2092380124476215</v>
       </c>
     </row>
@@ -5755,13 +5808,13 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="2" t="n">
         <v>0.2087277699243423</v>
       </c>
     </row>
@@ -5771,13 +5824,13 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="2" t="n">
         <v>0.2174850750035563</v>
       </c>
     </row>
@@ -5787,13 +5840,13 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="2" t="n">
         <v>0.2228509719785166</v>
       </c>
     </row>
@@ -5803,13 +5856,13 @@
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="2" t="n">
         <v>0.2232934460129385</v>
       </c>
     </row>
@@ -5819,13 +5872,13 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="2" t="n">
         <v>0.224466607514054</v>
       </c>
     </row>
@@ -5835,13 +5888,13 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="2" t="n">
         <v>0.2250776158334455</v>
       </c>
     </row>
@@ -5851,13 +5904,13 @@
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="2" t="n">
         <v>0.2261939343407518</v>
       </c>
     </row>
@@ -5867,13 +5920,13 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="2" t="n">
         <v>0.2269412326058056</v>
       </c>
     </row>
@@ -5883,13 +5936,13 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="2" t="n">
         <v>0.2271080482955739</v>
       </c>
     </row>
@@ -5899,13 +5952,13 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="2" t="n">
         <v>0.2295316544408021</v>
       </c>
     </row>
@@ -5915,13 +5968,13 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="2" t="n">
         <v>0.2302160465261997</v>
       </c>
     </row>
@@ -5931,13 +5984,13 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="2" t="n">
         <v>0.2297498347237704</v>
       </c>
     </row>
@@ -5947,13 +6000,13 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="2" t="n">
         <v>0.2271226287507213</v>
       </c>
     </row>
@@ -5963,13 +6016,13 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="3" t="n">
         <v>27.7</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="2" t="n">
         <v>0.2296623005084529</v>
       </c>
     </row>
@@ -5979,13 +6032,13 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="3" t="n">
         <v>27.7</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="2" t="n">
         <v>0.2337491979196922</v>
       </c>
     </row>
@@ -5995,13 +6048,13 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="3" t="n">
         <v>27.7</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="2" t="n">
         <v>0.231401365204684</v>
       </c>
     </row>
@@ -6011,13 +6064,13 @@
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="2" t="n">
         <v>0.2344587233260903</v>
       </c>
     </row>
@@ -6027,13 +6080,13 @@
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="2" t="n">
         <v>0.2337935444507051</v>
       </c>
     </row>
@@ -6043,13 +6096,13 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="2" t="n">
         <v>0.2313817636993311</v>
       </c>
     </row>
@@ -6059,13 +6112,13 @@
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="2" t="n">
         <v>0.229288359236466</v>
       </c>
     </row>
@@ -6075,13 +6128,13 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="2" t="n">
         <v>0.2296181638858062</v>
       </c>
     </row>
@@ -6091,13 +6144,13 @@
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="2" t="n">
         <v>0.2276679765581801</v>
       </c>
     </row>
@@ -6107,13 +6160,13 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="2" t="n">
         <v>0.22818312215479</v>
       </c>
     </row>
@@ -6123,13 +6176,13 @@
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="2" t="n">
         <v>0.2273303699795831</v>
       </c>
     </row>
@@ -6139,13 +6192,13 @@
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="2" t="n">
         <v>0.2223982205270898</v>
       </c>
     </row>
@@ -6155,13 +6208,13 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="2" t="n">
         <v>0.2269996991041931</v>
       </c>
     </row>
@@ -6171,13 +6224,13 @@
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="2" t="n">
         <v>0.2307998998903195</v>
       </c>
     </row>
@@ -6187,13 +6240,13 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="2" t="n">
         <v>0.2309106224989629</v>
       </c>
     </row>
@@ -6203,13 +6256,13 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="2" t="n">
         <v>0.2313516735410197</v>
       </c>
     </row>
@@ -6219,13 +6272,13 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="2" t="n">
         <v>0.2306294483365661</v>
       </c>
     </row>
@@ -6235,13 +6288,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="2" t="n">
         <v>0.2294983172850124</v>
       </c>
     </row>
@@ -6251,13 +6304,13 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="2" t="n">
         <v>0.2287026976988926</v>
       </c>
     </row>
@@ -6267,13 +6320,13 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="2" t="n">
         <v>0.2297852499560769</v>
       </c>
     </row>
@@ -6283,13 +6336,13 @@
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="2" t="n">
         <v>0.2319214393587778</v>
       </c>
     </row>
@@ -6299,13 +6352,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="2" t="n">
         <v>0.2320130487636571</v>
       </c>
     </row>
@@ -6315,13 +6368,13 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="2" t="n">
         <v>0.2307141182294245</v>
       </c>
     </row>
@@ -6331,13 +6384,13 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="2" t="n">
         <v>0.2281525216296589</v>
       </c>
     </row>
@@ -6347,13 +6400,13 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="2" t="n">
         <v>0.2336158570051581</v>
       </c>
     </row>
@@ -6363,13 +6416,13 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="2" t="n">
         <v>0.2378872739647667</v>
       </c>
     </row>
@@ -6379,13 +6432,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="2" t="n">
         <v>0.2399049316696376</v>
       </c>
     </row>
@@ -6395,13 +6448,13 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="2" t="n">
         <v>0.242166066134934</v>
       </c>
     </row>
@@ -6411,13 +6464,13 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="2" t="n">
         <v>0.2426195938894051</v>
       </c>
     </row>
@@ -6427,13 +6480,13 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="2" t="n">
         <v>0.243827945819321</v>
       </c>
     </row>
@@ -6443,13 +6496,13 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="2" t="n">
         <v>0.2435061603754021</v>
       </c>
     </row>
@@ -6459,13 +6512,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="2" t="n">
         <v>0.2446972358539269</v>
       </c>
     </row>
@@ -6475,13 +6528,13 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="2" t="n">
         <v>0.2461147734487857</v>
       </c>
     </row>
@@ -6491,13 +6544,13 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="2" t="n">
         <v>0.2481374902754657</v>
       </c>
     </row>
@@ -6507,14 +6560,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="D178" t="n">
-        <v>0.2476590850714911</v>
+      <c r="D178" s="2" t="n">
+        <v>0.2476337155964247</v>
       </c>
     </row>
     <row r="179">
@@ -6523,14 +6576,14 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="D179" t="n">
-        <v>0.2429894643675</v>
+      <c r="D179" s="2" t="n">
+        <v>0.2429690642487354</v>
       </c>
     </row>
     <row r="180">
@@ -6539,14 +6592,14 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D180" t="n">
-        <v>0.2473527913139845</v>
+      <c r="D180" s="2" t="n">
+        <v>0.2473434114465776</v>
       </c>
     </row>
     <row r="181">
@@ -6555,14 +6608,14 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="D181" t="n">
-        <v>0.2514593636361441</v>
+      <c r="D181" s="2" t="n">
+        <v>0.2514431486763121</v>
       </c>
     </row>
     <row r="182">
@@ -6571,14 +6624,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="D182" t="n">
-        <v>0.2482670266247457</v>
+      <c r="D182" s="2" t="n">
+        <v>0.2482663364677345</v>
       </c>
     </row>
     <row r="183">
@@ -6587,13 +6640,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="2" t="n">
         <v>0.2494826780720774</v>
       </c>
     </row>
@@ -6603,17 +6656,34 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="C184" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D184" t="n">
-        <v>0.2476130670072468</v>
+      <c r="C184" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>0.2480078302573855</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0.2450930472230976</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes Brutos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDC e Normalizados'!$A$1:$E$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Componentes Brutos'!$A$1:$D$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDC e Normalizados'!$A$1:$E$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Componentes Brutos'!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3556,10 +3556,10 @@
         <v>0.903225806451613</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.9922483704090016</v>
+        <v>0.9892219518293673</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.9610930183031318</v>
+        <v>0.9600842121099203</v>
       </c>
     </row>
     <row r="179">
@@ -3575,10 +3575,10 @@
         <v>0.9677419354838708</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.920472930072725</v>
+        <v>0.9199343400923999</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.9627382885188652</v>
+        <v>0.9625587585254235</v>
       </c>
     </row>
     <row r="180">
@@ -3594,10 +3594,10 @@
         <v>1</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.9877814324465222</v>
+        <v>0.9872659511807742</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.9959271441488408</v>
+        <v>0.995755317060258</v>
       </c>
     </row>
     <row r="181">
@@ -3632,10 +3632,10 @@
         <v>0.9393939393939393</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0.9534840917507833</v>
+        <v>0.9536895362579288</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.9603711084207899</v>
+        <v>0.9604395899231717</v>
       </c>
     </row>
     <row r="183">
@@ -3651,10 +3651,10 @@
         <v>1</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>0.9712941575502504</v>
+        <v>0.9714984708437086</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.9904313858500835</v>
+        <v>0.9904994902812362</v>
       </c>
     </row>
     <row r="184">
@@ -3670,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0.9496989605019228</v>
+        <v>0.9496890561364562</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.9832329868339743</v>
+        <v>0.9832296853788187</v>
       </c>
     </row>
     <row r="185">
@@ -3686,17 +3686,36 @@
         <v>1</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>0.9705882352941178</v>
+        <v>0.9428571428571431</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.9070197678750417</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.9592026677230532</v>
+        <v>0.9499589702440616</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>0.8876718413864001</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>0.9625572804621334</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E185"/>
+  <autoFilter ref="A1:E186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3707,7 +3726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6567,7 +6586,7 @@
         <v>6.9</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.2476337155964247</v>
+        <v>0.2474370301084636</v>
       </c>
     </row>
     <row r="179">
@@ -6583,7 +6602,7 @@
         <v>7.1</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.2429690642487354</v>
+        <v>0.2429340615449442</v>
       </c>
     </row>
     <row r="180">
@@ -6599,7 +6618,7 @@
         <v>7.2</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.2473434114465776</v>
+        <v>0.2473099105670328</v>
       </c>
     </row>
     <row r="181">
@@ -6631,7 +6650,7 @@
         <v>7.2</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0.2482663364677345</v>
+        <v>0.2482803673368081</v>
       </c>
     </row>
     <row r="183">
@@ -6647,7 +6666,7 @@
         <v>7.4</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>0.2494826780720774</v>
+        <v>0.2494966316847115</v>
       </c>
     </row>
     <row r="184">
@@ -6660,10 +6679,10 @@
         <v>28.5</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0.2480078302573855</v>
+        <v>0.2480071538369883</v>
       </c>
     </row>
     <row r="185">
@@ -6673,7 +6692,7 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="C185" s="3" t="n">
         <v>7.4</v>
@@ -6682,8 +6701,24 @@
         <v>0.2450930472230976</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>0.2437716771500794</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D185"/>
+  <autoFilter ref="A1:D186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes Brutos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDC e Normalizados'!$A$1:$E$186</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Componentes Brutos'!$A$1:$D$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDC e Normalizados'!$A$1:$E$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Componentes Brutos'!$A$1:$D$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,13 +24,16 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,14 +61,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -434,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -472,3250 +484,3269 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="3" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.2422116758283082</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="3" t="n">
         <v>0.1805589721566735</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.05882352941176449</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.8452633369830688</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <v>0.3619683494043387</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="3" t="n">
         <v>0.1363636363636367</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="3" t="n">
         <v>0.05882352941176449</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="3" t="n">
         <v>0.3983957219251337</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="3" t="n">
         <v>0.1818181818181829</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="3" t="n">
         <v>0.4331550802139041</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="3" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="3" t="n">
         <v>0.176470588235294</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.9680561565490443</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="3" t="n">
         <v>0.4572664906856885</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="3" t="n">
         <v>0.2727272727272735</v>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="3" t="n">
         <v>0.4634581105169344</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>0.2727272727272735</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.8496519028298313</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="3" t="n">
         <v>0.4133420781268781</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="3" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.8545129700067381</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="3" t="n">
         <v>0.3998109187009983</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="3" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.8905612560660224</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="3" t="n">
         <v>0.4118270140540931</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="3" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="3" t="n">
         <v>0.1176470588235295</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.8049778965668238</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="3" t="n">
         <v>0.3832992275543602</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="3" t="n">
         <v>0.4090909090909102</v>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.713339192629582</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="3" t="n">
         <v>0.374143367240164</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>0.5909090909090914</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.2830795797543156</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="3" t="n">
         <v>0.2913295568878023</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="3" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.5088844678235531</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="3" t="n">
         <v>0.4272039135169419</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="3" t="n">
         <v>0.8636363636363649</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.7821129659347716</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="3" t="n">
         <v>0.5485831098570455</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <v>0.8181818181818188</v>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.7541968664744032</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="3" t="n">
         <v>0.5241262282187407</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="3" t="n">
         <v>0.9090909090909094</v>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="3" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.9279450862400527</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="3" t="n">
         <v>0.629011998443654</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="3" t="n">
         <v>0.9090909090909094</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="3" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>0.9427410119443859</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="3" t="n">
         <v>0.6672773070117651</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="3" t="n">
         <v>0.9545454545454555</v>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="3" t="n">
         <v>0.1000000000000001</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.9794445854035727</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="3" t="n">
         <v>0.6779966799830094</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="3" t="n">
         <v>0.9545454545454555</v>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="3" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>0.9008948618122039</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="3" t="n">
         <v>0.6684801054525531</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.9730946232195287</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="3" t="n">
         <v>0.7410315410731761</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="3" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="3" t="n">
         <v>0.7666666666666666</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="3" t="n">
         <v>0.8333333333333326</v>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="3" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="3" t="n">
         <v>0.7111111111111108</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="3" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.9947231748960665</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="3" t="n">
         <v>0.6732410582986886</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.6194851476334481</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="3" t="n">
         <v>0.4842728269889271</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="3" t="n">
         <v>0.4583333333333335</v>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.814703135677309</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="3" t="n">
         <v>0.6076788230035475</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="3" t="n">
         <v>0.4999999999999993</v>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="3" t="n">
         <v>0.683333333333333</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="3" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.976211959824916</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="3" t="n">
         <v>0.7004039866083053</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="3" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="3" t="n">
         <v>0.7249999999999998</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="3" t="n">
         <v>0.7499999999999997</v>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="3" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>0.9766249935913064</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="3" t="n">
         <v>0.7755416645304353</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="3" t="n">
         <v>0.7499999999999997</v>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.9413080276142702</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="3" t="n">
         <v>0.7304360092047566</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>0.8704106420610767</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="3" t="n">
         <v>0.6956924362425809</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.8236933452801616</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="3" t="n">
         <v>0.680120003982276</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="3" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.8656792718241696</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="3" t="n">
         <v>0.6941153128302786</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="3" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>0.8375821687703922</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="3" t="n">
         <v>0.6541940562567973</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="3" t="n">
         <v>0.5833333333333337</v>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.6917450670248385</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="3" t="n">
         <v>0.5916928001193907</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="3" t="n">
         <v>0.4166666666666663</v>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="3" t="n">
         <v>0.4499999999999997</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>0.2724702528146602</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="3" t="n">
         <v>0.3797123064937755</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="3" t="n">
         <v>0.4166666666666663</v>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="3" t="n">
         <v>0.4499999999999997</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.4014108069632996</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="3" t="n">
         <v>0.4226924912099885</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.5102113018006617</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="3" t="n">
         <v>0.4145148783779982</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="3" t="n">
         <v>0.2916666666666661</v>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>0.424598883606307</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="3" t="n">
         <v>0.3720885167576577</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="3" t="n">
         <v>0.1250000000000002</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="3" t="n">
         <v>0.3500000000000001</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.4917212815545563</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="3" t="n">
         <v>0.3222404271848522</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>0.4561832144991673</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="3" t="n">
         <v>0.2853944048330557</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="3" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>0.3843416404621943</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="3" t="n">
         <v>0.2281138801540647</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="3" t="n">
         <v>0.04166666666666722</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="3" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>0.3187939095792203</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="3" t="n">
         <v>0.2201535254152958</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="3" t="n">
         <v>0.2083333333333331</v>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="3" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.2479810814968522</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="3" t="n">
         <v>0.2521048049433951</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="3" t="n">
         <v>0.2500000000000004</v>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="3" t="n">
         <v>0.1974502257562492</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="3" t="n">
         <v>0.2324834085854165</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="3" t="n">
         <v>0.1666666666666674</v>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="3" t="n">
         <v>0.1999999999999997</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.1990704171206821</v>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="3" t="n">
         <v>0.1885790279291164</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="3" t="n">
         <v>0.04166666666666722</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="3" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.09469954379412228</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="3" t="n">
         <v>0.09545540348692981</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="3" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" s="3" t="n">
         <v>0.01666666666666661</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="3" t="n">
         <v>0.04999999999999982</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="3" t="n">
         <v>0.0919668901002043</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" s="3" t="n">
         <v>0.04732229670006805</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>0.2606429582478396</v>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="3" t="n">
         <v>0.08688098608261319</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" s="3" t="n">
         <v>0.03703703703703753</v>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="3" t="n">
         <v>0.1986749147155459</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="3" t="n">
         <v>0.07857065058419449</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="3" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="3" t="n">
         <v>0.2344603022598383</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="3" t="n">
         <v>0.1151904711236498</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="3" t="n">
         <v>0.2222222222222225</v>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>0.1789173120196445</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="3" t="n">
         <v>0.1337131780806223</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" s="3" t="n">
         <v>0.37037037037037</v>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>0.2052644274097824</v>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" s="3" t="n">
         <v>0.1918782659267174</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" s="3" t="n">
         <v>0.185185185185185</v>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" s="3" t="n">
         <v>0.04545454545454529</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="3" t="n">
         <v>0.1213751722158816</v>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="3" t="n">
         <v>0.1173383009518706</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" s="3" t="n">
         <v>0.07407407407407506</v>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" s="3" t="n">
         <v>0.04545454545454529</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="3" t="n">
         <v>0.06988382567382279</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="3" t="n">
         <v>0.06313748173414771</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" s="3" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="3" t="n">
         <v>0.05070704636073997</v>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E92" s="3" t="n">
         <v>0.05393938582395041</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="3" t="n">
         <v>0.1111111111111113</v>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="3" t="n">
         <v>0.08470716949469945</v>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="3" t="n">
         <v>0.0652727602019369</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="3" t="n">
         <v>0.1481481481481488</v>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>0.01775627016430798</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="3" t="n">
         <v>0.05530147277081892</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" s="3" t="n">
         <v>0.25925925925926</v>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E95" s="3" t="n">
         <v>0.08641975308642001</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" s="3" t="n">
         <v>0.3333333333333338</v>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" s="3" t="n">
         <v>0.1274114744239928</v>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="3" t="n">
         <v>0.1535816025857755</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="3" t="n">
         <v>0.4074074074074075</v>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="3" t="n">
         <v>0.251827182758644</v>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="3" t="n">
         <v>0.2197448633886838</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" s="3" t="n">
         <v>0.4074074074074075</v>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="3" t="n">
         <v>0.2403322312375094</v>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" s="3" t="n">
         <v>0.215913212881639</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" s="3" t="n">
         <v>0.5925925925925924</v>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="3" t="n">
         <v>0.2958785670844841</v>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="3" t="n">
         <v>0.2961570532256922</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" s="3" t="n">
         <v>0.7407407407407399</v>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" s="3" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="3" t="n">
         <v>0.3019317271839393</v>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="3" t="n">
         <v>0.3614463781971153</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" s="3" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.3650606198010092</v>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" s="3" t="n">
         <v>0.4689090954892254</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" s="3" t="n">
         <v>0.8749999999999994</v>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" s="3" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="3" t="n">
         <v>0.2989804724093655</v>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="3" t="n">
         <v>0.4052157130253439</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" s="3" t="n">
         <v>0.8749999999999994</v>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" s="3" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="3" t="n">
         <v>0.2942301618472238</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="3" t="n">
         <v>0.4036322761712967</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" s="3" t="n">
         <v>0.6249999999999994</v>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" s="3" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" s="3" t="n">
         <v>0.2955600487797549</v>
       </c>
-      <c r="E104" s="2" t="n">
+      <c r="E104" s="3" t="n">
         <v>0.3485200162599181</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" s="3" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" s="3" t="n">
         <v>0.2544007488826512</v>
       </c>
-      <c r="E105" s="2" t="n">
+      <c r="E105" s="3" t="n">
         <v>0.2931335829608837</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" s="3" t="n">
         <v>0.3437500000000001</v>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="3" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" s="3" t="n">
         <v>0.210876468714607</v>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E106" s="3" t="n">
         <v>0.2265421562382023</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" s="3" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" s="3" t="n">
         <v>0.1249999999999999</v>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D107" s="3" t="n">
         <v>0.03320867850220396</v>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" s="3" t="n">
         <v>0.1256528928340682</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" s="3" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" s="3" t="n">
         <v>0.0833333333333334</v>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" s="3" t="n">
         <v>0.1143472688322961</v>
       </c>
-      <c r="E108" s="2" t="n">
+      <c r="E108" s="3" t="n">
         <v>0.1388102007218767</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" s="3" t="n">
         <v>0.2187500000000007</v>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" s="3" t="n">
         <v>0.1666666666666668</v>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D109" s="3" t="n">
         <v>0.2186032841721531</v>
       </c>
-      <c r="E109" s="2" t="n">
+      <c r="E109" s="3" t="n">
         <v>0.2013399836129402</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" s="3" t="n">
         <v>0.5624999999999998</v>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" s="3" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" s="3" t="n">
         <v>0.2608852353232828</v>
       </c>
-      <c r="E110" s="2" t="n">
+      <c r="E110" s="3" t="n">
         <v>0.3439061895522053</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" s="3" t="n">
         <v>0.4062499999999999</v>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" s="3" t="n">
         <v>0.3333333333333332</v>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" s="3" t="n">
         <v>0.4496545779210505</v>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E111" s="3" t="n">
         <v>0.3964126370847945</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" s="3" t="n">
         <v>0.3750000000000001</v>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" s="3" t="n">
         <v>0.3358003984846665</v>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E112" s="3" t="n">
         <v>0.2369334661615556</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" s="3" t="n">
         <v>0.2500000000000002</v>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" s="3" t="n">
         <v>0.1839690628946757</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E113" s="3" t="n">
         <v>0.1446563542982253</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" s="3" t="n">
         <v>0.1666666666666668</v>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" s="3" t="n">
         <v>0.02988643543015799</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="3" t="n">
         <v>0.0655177006989416</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" s="3" t="n">
         <v>0.04166666666666688</v>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E115" s="3" t="n">
         <v>0.01388888888888896</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" s="3" t="n">
         <v>0.03773584905660363</v>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E116" s="3" t="n">
         <v>0.01257861635220121</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" s="3" t="n">
         <v>0.1320754716981131</v>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E117" s="3" t="n">
         <v>0.04402515723270436</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" s="3" t="n">
         <v>0.2830188679245282</v>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E118" s="3" t="n">
         <v>0.09433962264150941</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" s="3" t="n">
         <v>0.3773584905660377</v>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D119" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" s="3" t="n">
         <v>0.1257861635220126</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" s="3" t="n">
         <v>0.452830188679245</v>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D120" s="3" t="n">
         <v>0.08432386816264849</v>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E120" s="3" t="n">
         <v>0.1790513522806312</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" s="3" t="n">
         <v>0.4150943396226413</v>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D121" s="3" t="n">
         <v>0.1797646780629271</v>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E121" s="3" t="n">
         <v>0.1982863392285228</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" s="3" t="n">
         <v>0.4716981132075471</v>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="2" t="n">
+      <c r="D122" s="3" t="n">
         <v>0.222881401686199</v>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E122" s="3" t="n">
         <v>0.231526504964582</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" s="3" t="n">
         <v>0.4905660377358486</v>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D123" s="3" t="n">
         <v>0.2578785365837941</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E123" s="3" t="n">
         <v>0.2494815247732142</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" s="3" t="n">
         <v>0.5660377358490565</v>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" s="3" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D124" s="3" t="n">
         <v>0.2621361910098082</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E124" s="3" t="n">
         <v>0.2868106637916646</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" s="3" t="n">
         <v>0.6037735849056601</v>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D125" s="3" t="n">
         <v>0.2912782721622858</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" s="3" t="n">
         <v>0.2983506190226486</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" s="3" t="n">
         <v>0.660377358490566</v>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" s="3" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D126" s="3" t="n">
         <v>0.3010636222012054</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" s="3" t="n">
         <v>0.3312330150693002</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" s="3" t="n">
         <v>0.7169811320754718</v>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="3" t="n">
         <v>0.0322580645161292</v>
       </c>
-      <c r="D127" s="2" t="n">
+      <c r="D127" s="3" t="n">
         <v>0.3704465919714397</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E127" s="3" t="n">
         <v>0.3732285961876802</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" s="3" t="n">
         <v>0.8867924528301884</v>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" s="3" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D128" s="3" t="n">
         <v>0.4501251535328989</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="3" t="n">
         <v>0.4671445784651151</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" s="3" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D129" s="3" t="n">
         <v>0.529685447230225</v>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" s="3" t="n">
         <v>0.5314005254208277</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" s="3" t="n">
         <v>0.0645161290322581</v>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.5410085340371137</v>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E130" s="3" t="n">
         <v>0.5351748876897906</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" s="3" t="n">
         <v>0.09677419354838732</v>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" s="3" t="n">
         <v>0.5304280387025574</v>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="3" t="n">
         <v>0.5424007440836482</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" s="3" t="n">
         <v>0.1935483870967743</v>
       </c>
-      <c r="D132" s="2" t="n">
+      <c r="D132" s="3" t="n">
         <v>0.712021342487658</v>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="3" t="n">
         <v>0.6351899098614774</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" s="3" t="n">
         <v>0.9354838709677421</v>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="3" t="n">
         <v>0.2258064516129032</v>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D133" s="3" t="n">
         <v>0.8232897008055995</v>
       </c>
-      <c r="E133" s="2" t="n">
+      <c r="E133" s="3" t="n">
         <v>0.6615266744620817</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" s="3" t="n">
         <v>0.9032258064516127</v>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" s="3" t="n">
         <v>0.2580645161290324</v>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" s="3" t="n">
         <v>0.8324649346273065</v>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E134" s="3" t="n">
         <v>0.6645850857359838</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" s="3" t="n">
         <v>0.9354838709677421</v>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" s="3" t="n">
         <v>0.3225806451612903</v>
       </c>
-      <c r="D135" s="2" t="n">
+      <c r="D135" s="3" t="n">
         <v>0.8567918560870487</v>
       </c>
-      <c r="E135" s="2" t="n">
+      <c r="E135" s="3" t="n">
         <v>0.704952124072027</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" s="3" t="n">
         <v>0.9032258064516127</v>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" s="3" t="n">
         <v>0.4193548387096776</v>
       </c>
-      <c r="D136" s="2" t="n">
+      <c r="D136" s="3" t="n">
         <v>0.8694618519767494</v>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" s="3" t="n">
         <v>0.7306808323793467</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" s="3" t="n">
         <v>0.3870967741935484</v>
       </c>
-      <c r="D137" s="2" t="n">
+      <c r="D137" s="3" t="n">
         <v>0.89261006526663</v>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="E137" s="3" t="n">
         <v>0.7599022798200595</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D138" s="3" t="n">
         <v>0.9081061978823698</v>
       </c>
-      <c r="E138" s="2" t="n">
+      <c r="E138" s="3" t="n">
         <v>0.7973257218747684</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D139" s="2" t="n">
+      <c r="D139" s="3" t="n">
         <v>0.9115653228019891</v>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E139" s="3" t="n">
         <v>0.8092314516866845</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" s="3" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D140" s="3" t="n">
         <v>0.9618217250861214</v>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E140" s="3" t="n">
         <v>0.8367362739534383</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" s="3" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D141" s="2" t="n">
+      <c r="D141" s="3" t="n">
         <v>0.9760134220462652</v>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="E141" s="3" t="n">
         <v>0.8522195277788627</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" s="3" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D142" s="2" t="n">
+      <c r="D142" s="3" t="n">
         <v>0.9663459569184722</v>
       </c>
-      <c r="E142" s="2" t="n">
+      <c r="E142" s="3" t="n">
         <v>0.8489970394029317</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B143" s="2" t="n">
+      <c r="B143" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="C143" s="3" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D143" s="3" t="n">
         <v>0.9118676661595573</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="3" t="n">
         <v>0.841590297322003</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B144" s="2" t="n">
+      <c r="B144" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C144" s="2" t="n">
+      <c r="C144" s="3" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D144" s="2" t="n">
+      <c r="D144" s="3" t="n">
         <v>0.9645308291811198</v>
       </c>
-      <c r="E144" s="2" t="n">
+      <c r="E144" s="3" t="n">
         <v>0.8806500613399432</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n">
+      <c r="B145" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="C145" s="3" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D145" s="2" t="n">
+      <c r="D145" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E145" s="2" t="n">
+      <c r="E145" s="3" t="n">
         <v>0.89247311827957</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n">
+      <c r="B146" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="3" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D146" s="2" t="n">
+      <c r="D146" s="3" t="n">
         <v>0.9536012688232502</v>
       </c>
-      <c r="E146" s="2" t="n">
+      <c r="E146" s="3" t="n">
         <v>0.8770068745539866</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B147" s="2" t="n">
+      <c r="B147" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="3" t="n">
         <v>0.7096774193548386</v>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D147" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E147" s="3" t="n">
         <v>0.9032258064516129</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B148" s="2" t="n">
+      <c r="B148" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="C148" s="3" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="D148" s="2" t="n">
+      <c r="D148" s="3" t="n">
         <v>0.9870362672921551</v>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" s="3" t="n">
         <v>0.9204099385597506</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n">
+      <c r="B149" s="3" t="n">
         <v>0.9756097560975611</v>
       </c>
-      <c r="C149" s="2" t="n">
+      <c r="C149" s="3" t="n">
         <v>0.7419354838709679</v>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D149" s="3" t="n">
         <v>0.9400328488618431</v>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E149" s="3" t="n">
         <v>0.8858593629434574</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n">
+      <c r="B150" s="3" t="n">
         <v>0.9146341463414634</v>
       </c>
-      <c r="C150" s="2" t="n">
+      <c r="C150" s="3" t="n">
         <v>0.7096774193548386</v>
       </c>
-      <c r="D150" s="2" t="n">
+      <c r="D150" s="3" t="n">
         <v>0.8992342954046627</v>
       </c>
-      <c r="E150" s="2" t="n">
+      <c r="E150" s="3" t="n">
         <v>0.8411819537003216</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n">
+      <c r="B151" s="3" t="n">
         <v>0.8658536585365851</v>
       </c>
-      <c r="C151" s="2" t="n">
+      <c r="C151" s="3" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D151" s="2" t="n">
+      <c r="D151" s="3" t="n">
         <v>0.905661888760471</v>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E151" s="3" t="n">
         <v>0.8163116340452552</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B152" s="3" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C152" s="2" t="n">
+      <c r="C152" s="3" t="n">
         <v>0.6451612903225805</v>
       </c>
-      <c r="D152" s="2" t="n">
+      <c r="D152" s="3" t="n">
         <v>0.8676545073159999</v>
       </c>
-      <c r="E152" s="2" t="n">
+      <c r="E152" s="3" t="n">
         <v>0.7888247780746488</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B153" s="3" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C153" s="2" t="n">
+      <c r="C153" s="3" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="D153" s="2" t="n">
+      <c r="D153" s="3" t="n">
         <v>0.8776942275584794</v>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E153" s="3" t="n">
         <v>0.7814186633167658</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B154" s="2" t="n">
+      <c r="B154" s="3" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C154" s="2" t="n">
+      <c r="C154" s="3" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D154" s="3" t="n">
         <v>0.8610748614383315</v>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="3" t="n">
         <v>0.7529310644867871</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B155" s="2" t="n">
+      <c r="B155" s="3" t="n">
         <v>0.7317073170731708</v>
       </c>
-      <c r="C155" s="2" t="n">
+      <c r="C155" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D155" s="3" t="n">
         <v>0.7649517439682593</v>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E155" s="3" t="n">
         <v>0.670929364433165</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B156" s="2" t="n">
+      <c r="B156" s="3" t="n">
         <v>0.7195121951219511</v>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D156" s="2" t="n">
+      <c r="D156" s="3" t="n">
         <v>0.8546303861228126</v>
       </c>
-      <c r="E156" s="2" t="n">
+      <c r="E156" s="3" t="n">
         <v>0.6967572045009428</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n">
+      <c r="B157" s="3" t="n">
         <v>0.7317073170731708</v>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="C157" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D157" s="3" t="n">
         <v>0.9286928511987693</v>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" s="3" t="n">
         <v>0.7255097335100015</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n">
+      <c r="B158" s="3" t="n">
         <v>0.7682926829268294</v>
       </c>
-      <c r="C158" s="2" t="n">
+      <c r="C158" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D158" s="2" t="n">
+      <c r="D158" s="3" t="n">
         <v>0.9308507343731816</v>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="E158" s="3" t="n">
         <v>0.7276714616806488</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B159" s="2" t="n">
+      <c r="B159" s="3" t="n">
         <v>0.7682926829268294</v>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D159" s="2" t="n">
+      <c r="D159" s="3" t="n">
         <v>0.9394464189797158</v>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" s="3" t="n">
         <v>0.7305366898828268</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B160" s="2" t="n">
+      <c r="B160" s="3" t="n">
         <v>0.7560975609756098</v>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="C160" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D160" s="2" t="n">
+      <c r="D160" s="3" t="n">
         <v>0.9253709050813183</v>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" s="3" t="n">
         <v>0.732532499438331</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n">
+      <c r="B161" s="3" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D161" s="2" t="n">
+      <c r="D161" s="3" t="n">
         <v>0.9033261872580214</v>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" s="3" t="n">
         <v>0.7306917345934815</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n">
+      <c r="B162" s="3" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="C162" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D162" s="2" t="n">
+      <c r="D162" s="3" t="n">
         <v>0.8878202834579203</v>
       </c>
-      <c r="E162" s="2" t="n">
+      <c r="E162" s="3" t="n">
         <v>0.7295881406438544</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B163" s="2" t="n">
+      <c r="B163" s="3" t="n">
         <v>0.8414634146341462</v>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="C163" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D163" s="2" t="n">
+      <c r="D163" s="3" t="n">
         <v>0.9089182446586339</v>
       </c>
-      <c r="E163" s="2" t="n">
+      <c r="E163" s="3" t="n">
         <v>0.7555035638502815</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B164" s="2" t="n">
+      <c r="B164" s="3" t="n">
         <v>0.8170731707317073</v>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="C164" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D164" s="2" t="n">
+      <c r="D164" s="3" t="n">
         <v>0.950550637770796</v>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="E164" s="3" t="n">
         <v>0.7612509469201892</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B165" s="2" t="n">
+      <c r="B165" s="3" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="C165" s="3" t="n">
         <v>0.4838709677419354</v>
       </c>
-      <c r="D165" s="2" t="n">
+      <c r="D165" s="3" t="n">
         <v>0.9523360219468819</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" s="3" t="n">
         <v>0.747028346156435</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B166" s="2" t="n">
+      <c r="B166" s="3" t="n">
         <v>0.8048780487804876</v>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="3" t="n">
         <v>0.4516129032258065</v>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D166" s="3" t="n">
         <v>0.9270210444649277</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E166" s="3" t="n">
         <v>0.7278373321570739</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n">
+      <c r="B167" s="3" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="3" t="n">
         <v>0.4193548387096776</v>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D167" s="3" t="n">
         <v>0.8770978510901344</v>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E167" s="3" t="n">
         <v>0.7167037421283927</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n">
+      <c r="B168" s="3" t="n">
         <v>0.8414634146341462</v>
       </c>
-      <c r="C168" s="2" t="n">
+      <c r="C168" s="3" t="n">
         <v>0.5161290322580646</v>
       </c>
-      <c r="D168" s="2" t="n">
+      <c r="D168" s="3" t="n">
         <v>0.9835733002093877</v>
       </c>
-      <c r="E168" s="2" t="n">
+      <c r="E168" s="3" t="n">
         <v>0.7803885823671995</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n">
+      <c r="B169" s="3" t="n">
         <v>0.8536585365853659</v>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="3" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="D169" s="2" t="n">
+      <c r="D169" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="E169" s="3" t="n">
         <v>0.8006818777865199</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B170" s="2" t="n">
+      <c r="B170" s="3" t="n">
         <v>0.8780487804878049</v>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="C170" s="3" t="n">
         <v>0.5806451612903227</v>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D170" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="E170" s="3" t="n">
         <v>0.8195646472593759</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B171" s="2" t="n">
+      <c r="B171" s="3" t="n">
         <v>0.8902439024390245</v>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="C171" s="3" t="n">
         <v>0.6774193548387097</v>
       </c>
-      <c r="D171" s="2" t="n">
+      <c r="D171" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E171" s="2" t="n">
+      <c r="E171" s="3" t="n">
         <v>0.8558877524259114</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B172" s="2" t="n">
+      <c r="B172" s="3" t="n">
         <v>0.9024390243902438</v>
       </c>
-      <c r="C172" s="2" t="n">
+      <c r="C172" s="3" t="n">
         <v>0.7419354838709679</v>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D172" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="3" t="n">
         <v>0.8814581694204039</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B173" s="2" t="n">
+      <c r="B173" s="3" t="n">
         <v>0.9024390243902438</v>
       </c>
-      <c r="C173" s="2" t="n">
+      <c r="C173" s="3" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="D173" s="2" t="n">
+      <c r="D173" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="2" t="n">
+      <c r="E173" s="3" t="n">
         <v>0.8922108575924469</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B174" s="2" t="n">
+      <c r="B174" s="3" t="n">
         <v>0.9146341463414634</v>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C174" s="3" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="D174" s="2" t="n">
+      <c r="D174" s="3" t="n">
         <v>0.994697007603812</v>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E174" s="3" t="n">
         <v>0.9160136104548767</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B175" s="2" t="n">
+      <c r="B175" s="3" t="n">
         <v>0.9512195121951221</v>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="C175" s="3" t="n">
         <v>0.9354838709677419</v>
       </c>
-      <c r="D175" s="2" t="n">
+      <c r="D175" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="E175" s="3" t="n">
         <v>0.962234461054288</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n">
+      <c r="B176" s="3" t="n">
         <v>0.9756097560975611</v>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="C176" s="3" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D176" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E176" s="3" t="n">
         <v>0.9596118541830579</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B177" s="2" t="n">
+      <c r="B177" s="3" t="n">
         <v>0.9878048780487804</v>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="C177" s="3" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D177" s="2" t="n">
+      <c r="D177" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="E177" s="3" t="n">
         <v>0.9636768948334645</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B178" s="2" t="n">
+      <c r="B178" s="3" t="n">
         <v>0.9878048780487804</v>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="C178" s="3" t="n">
         <v>0.903225806451613</v>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D178" s="3" t="n">
         <v>0.9892219518293673</v>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="E178" s="3" t="n">
         <v>0.9600842121099203</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B179" s="2" t="n">
+      <c r="B179" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="3" t="n">
         <v>0.9677419354838708</v>
       </c>
-      <c r="D179" s="2" t="n">
+      <c r="D179" s="3" t="n">
         <v>0.9199343400923999</v>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="E179" s="3" t="n">
         <v>0.9625587585254235</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B180" s="2" t="n">
+      <c r="B180" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D180" s="2" t="n">
+      <c r="D180" s="3" t="n">
         <v>0.9872659511807742</v>
       </c>
-      <c r="E180" s="2" t="n">
+      <c r="E180" s="3" t="n">
         <v>0.995755317060258</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B181" s="2" t="n">
+      <c r="B181" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="C181" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D181" s="2" t="n">
+      <c r="D181" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E181" s="2" t="n">
+      <c r="E181" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B182" s="2" t="n">
+      <c r="B182" s="3" t="n">
         <v>0.9882352941176469</v>
       </c>
-      <c r="C182" s="2" t="n">
+      <c r="C182" s="3" t="n">
         <v>0.9393939393939393</v>
       </c>
-      <c r="D182" s="2" t="n">
+      <c r="D182" s="3" t="n">
         <v>0.9536895362579288</v>
       </c>
-      <c r="E182" s="2" t="n">
+      <c r="E182" s="3" t="n">
         <v>0.9604395899231717</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B183" s="2" t="n">
+      <c r="B183" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="C183" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D183" s="3" t="n">
         <v>0.9714984708437086</v>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="E183" s="3" t="n">
         <v>0.9904994902812362</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B184" s="2" t="n">
+      <c r="B184" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C184" s="2" t="n">
+      <c r="C184" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D184" s="2" t="n">
+      <c r="D184" s="3" t="n">
         <v>0.9496890561364562</v>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" s="3" t="n">
         <v>0.9832296853788187</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B185" s="2" t="n">
+      <c r="B185" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C185" s="3" t="n">
         <v>0.9428571428571431</v>
       </c>
-      <c r="D185" s="2" t="n">
-        <v>0.9070197678750417</v>
-      </c>
-      <c r="E185" s="2" t="n">
-        <v>0.9499589702440616</v>
+      <c r="D185" s="3" t="n">
+        <v>0.9080806237326325</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>0.9503125888632585</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B186" s="2" t="n">
+      <c r="B186" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C186" s="2" t="n">
+      <c r="C186" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D186" s="2" t="n">
-        <v>0.8876718413864001</v>
-      </c>
-      <c r="E186" s="2" t="n">
-        <v>0.9625572804621334</v>
+      <c r="D186" s="3" t="n">
+        <v>0.887710611136905</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>0.9625702037123016</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0.8984330841597294</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>0.9661443613865766</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E186"/>
+  <autoFilter ref="A1:E187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3726,7 +3757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3758,2967 +3789,2983 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.2144837064952339</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.216318931938421</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.2155671126202916</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.2158826655184728</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.2133800314704837</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.2142054660256966</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.2163096789499437</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.2179910005812397</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>6.6</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.2182622171978539</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>6.7</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.2133141087974606</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.21806653595598</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.2219530188435359</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.2215058239527761</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.2221233325942454</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.220769753883536</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.2197200510871163</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.2177195914744852</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.2163159091483287</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.2204091315317143</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.2193257789363551</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.2184516937304613</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.2113327832216916</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.2105058800605199</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>6.7</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.2146924625203246</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>6.6</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.214597665058659</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.215024108630904</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>6.6</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.2136504283411237</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.2142377228564658</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.2123923622042895</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.2130640498279781</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.2161353832177457</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.21538183222886</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.2149883683635729</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.2094029707921079</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.212483990941346</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.2201550262566146</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.2223286212692439</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.2252691174230988</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.2247622917189485</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.2272836840920228</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.2245953528713353</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.2246822722198572</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.2253268412878366</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.2237965497733879</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.2221579843811103</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.2144646355987552</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.2185021880640406</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="4" t="n">
         <v>24.1</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.2233877085041337</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.2228885487332309</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.2259952908372311</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>0.2262598525427572</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.2269161386168632</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>0.2255116135295384</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.2268025967635851</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="4" t="n">
         <v>24.6</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>0.2277693945106953</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.2285807873414926</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.2284795893576861</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.2212833433084906</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.2250271980703358</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
+      <c r="B61" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>0.2290960142036387</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.2286275552957955</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>0.2313727950217048</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>0.2308592502395401</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.2300833427047019</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>0.2285257396057603</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.2274993688070017</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.2284217922332903</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>0.227804503817838</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.2246004883263343</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>0.2153890943542398</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.2182218956649522</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.2206122234126222</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>0.2187313336330215</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.2202060009178136</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>0.2194252358311471</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>0.2178468890771772</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>0.2164068169510294</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.2148510715648591</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="3" t="n">
         <v>0.2137409175460669</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.2137765128655618</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.2114835031238878</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>0.2030377503203539</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="3" t="n">
         <v>0.2056436362623874</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>0.2104230801933988</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="C86" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="3" t="n">
         <v>0.208667212909856</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="3" t="n">
         <v>0.2096811934655787</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>0.2081073803542761</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
+      <c r="B89" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C89" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>0.2088539270466073</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B90" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="C90" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="3" t="n">
         <v>0.2064769212507251</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B91" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C91" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="3" t="n">
         <v>0.2050179116447231</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B92" s="3" t="n">
+      <c r="B92" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="C92" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="3" t="n">
         <v>0.204474536745659</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B93" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="3" t="n">
         <v>0.2054379317545111</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C94" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>0.2035408750291889</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B95" s="3" t="n">
+      <c r="B95" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="C95" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.1987779985246286</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
+      <c r="B96" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="C96" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" s="3" t="n">
         <v>0.2029309496048711</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B97" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="3" t="n">
         <v>0.2069862542990786</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="C98" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="3" t="n">
         <v>0.2066115786935035</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="C99" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="3" t="n">
         <v>0.2084221002065939</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
+      <c r="B100" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="C100" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="3" t="n">
         <v>0.2086194017281998</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B101" s="3" t="n">
+      <c r="B101" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="C101" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.210677075136139</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n">
+      <c r="B102" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="C102" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="3" t="n">
         <v>0.2085232061794116</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B103" s="3" t="n">
+      <c r="B103" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="C103" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="3" t="n">
         <v>0.2083683707733407</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="C104" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" s="3" t="n">
         <v>0.2084117181672706</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B105" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="C105" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" s="3" t="n">
         <v>0.2070701391631624</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B106" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="C106" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" s="3" t="n">
         <v>0.2056514741084033</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B107" s="3" t="n">
+      <c r="B107" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="C107" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D107" s="3" t="n">
         <v>0.1998604286423448</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B108" s="3" t="n">
+      <c r="B108" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="C108" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" s="3" t="n">
         <v>0.2025051244822138</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B109" s="3" t="n">
+      <c r="B109" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="C109" s="3" t="n">
+      <c r="C109" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D109" s="3" t="n">
         <v>0.2059033280858125</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B110" s="3" t="n">
+      <c r="B110" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="C110" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" s="3" t="n">
         <v>0.2072814996790829</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B111" s="3" t="n">
+      <c r="B111" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="C111" s="3" t="n">
+      <c r="C111" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" s="3" t="n">
         <v>0.2134343979859439</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B112" s="3" t="n">
+      <c r="B112" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="C112" s="3" t="n">
+      <c r="C112" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" s="3" t="n">
         <v>0.2097233441768734</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B113" s="3" t="n">
+      <c r="B113" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="C113" s="3" t="n">
+      <c r="C113" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" s="3" t="n">
         <v>0.2047744326914384</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B114" s="3" t="n">
+      <c r="B114" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="C114" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" s="3" t="n">
         <v>0.1997521408054976</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B115" s="3" t="n">
+      <c r="B115" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="C115" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" s="3" t="n">
         <v>0.195092288385341</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B116" s="3" t="n">
+      <c r="B116" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C116" s="3" t="n">
+      <c r="C116" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" s="3" t="n">
         <v>0.1926571603789215</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B117" s="3" t="n">
+      <c r="B117" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="C117" s="3" t="n">
+      <c r="C117" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D117" s="3" t="n">
         <v>0.1912005200489418</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n">
+      <c r="B118" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="C118" s="4" t="n">
         <v>4.4</v>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" s="3" t="n">
         <v>0.1865992586106102</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B119" s="3" t="n">
+      <c r="B119" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="C119" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D119" s="3" t="n">
         <v>0.1831479712166515</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B120" s="3" t="n">
+      <c r="B120" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="C120" s="3" t="n">
+      <c r="C120" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D120" s="3" t="n">
         <v>0.1872144749013558</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B121" s="3" t="n">
+      <c r="B121" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C121" s="3" t="n">
+      <c r="C121" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D121" s="3" t="n">
         <v>0.1918170911426083</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B122" s="3" t="n">
+      <c r="B122" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="C122" s="3" t="n">
+      <c r="C122" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="D122" s="2" t="n">
+      <c r="D122" s="3" t="n">
         <v>0.1938963875423917</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B123" s="3" t="n">
+      <c r="B123" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="C123" s="3" t="n">
+      <c r="C123" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D123" s="3" t="n">
         <v>0.1955841182065099</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B124" s="3" t="n">
+      <c r="B124" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="C124" s="3" t="n">
+      <c r="C124" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D124" s="3" t="n">
         <v>0.1957894428410273</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B125" s="3" t="n">
+      <c r="B125" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C125" s="3" t="n">
+      <c r="C125" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D125" s="3" t="n">
         <v>0.1971948145699181</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B126" s="3" t="n">
+      <c r="B126" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="C126" s="3" t="n">
+      <c r="C126" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D126" s="3" t="n">
         <v>0.1976667113514158</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B127" s="3" t="n">
+      <c r="B127" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="C127" s="3" t="n">
+      <c r="C127" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="D127" s="2" t="n">
+      <c r="D127" s="3" t="n">
         <v>0.2010126928436566</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B128" s="3" t="n">
+      <c r="B128" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="C128" s="3" t="n">
+      <c r="C128" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D128" s="3" t="n">
         <v>0.2048551774359981</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B129" s="3" t="n">
+      <c r="B129" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="C129" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D129" s="3" t="n">
         <v>0.2086919585814299</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B130" s="3" t="n">
+      <c r="B130" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="C130" s="3" t="n">
+      <c r="C130" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.2092380124476215</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n">
+      <c r="B131" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="C131" s="3" t="n">
+      <c r="C131" s="4" t="n">
         <v>4.4</v>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" s="3" t="n">
         <v>0.2087277699243423</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B132" s="3" t="n">
+      <c r="B132" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="C132" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="D132" s="2" t="n">
+      <c r="D132" s="3" t="n">
         <v>0.2174850750035563</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B133" s="3" t="n">
+      <c r="B133" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="C133" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D133" s="3" t="n">
         <v>0.2228509719785166</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B134" s="3" t="n">
+      <c r="B134" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="C134" s="3" t="n">
+      <c r="C134" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" s="3" t="n">
         <v>0.2232934460129385</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B135" s="3" t="n">
+      <c r="B135" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="C135" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="D135" s="2" t="n">
+      <c r="D135" s="3" t="n">
         <v>0.224466607514054</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B136" s="3" t="n">
+      <c r="B136" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="C136" s="3" t="n">
+      <c r="C136" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D136" s="2" t="n">
+      <c r="D136" s="3" t="n">
         <v>0.2250776158334455</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B137" s="3" t="n">
+      <c r="B137" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C137" s="3" t="n">
+      <c r="C137" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="D137" s="2" t="n">
+      <c r="D137" s="3" t="n">
         <v>0.2261939343407518</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B138" s="3" t="n">
+      <c r="B138" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="C138" s="3" t="n">
+      <c r="C138" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D138" s="3" t="n">
         <v>0.2269412326058056</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B139" s="3" t="n">
+      <c r="B139" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="C139" s="3" t="n">
+      <c r="C139" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D139" s="2" t="n">
+      <c r="D139" s="3" t="n">
         <v>0.2271080482955739</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B140" s="3" t="n">
+      <c r="B140" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="C140" s="3" t="n">
+      <c r="C140" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D140" s="3" t="n">
         <v>0.2295316544408021</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B141" s="3" t="n">
+      <c r="B141" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="C141" s="3" t="n">
+      <c r="C141" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D141" s="2" t="n">
+      <c r="D141" s="3" t="n">
         <v>0.2302160465261997</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B142" s="3" t="n">
+      <c r="B142" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="C142" s="3" t="n">
+      <c r="C142" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D142" s="2" t="n">
+      <c r="D142" s="3" t="n">
         <v>0.2297498347237704</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B143" s="3" t="n">
+      <c r="B143" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="C143" s="3" t="n">
+      <c r="C143" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D143" s="3" t="n">
         <v>0.2271226287507213</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B144" s="3" t="n">
+      <c r="B144" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="C144" s="3" t="n">
+      <c r="C144" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D144" s="2" t="n">
+      <c r="D144" s="3" t="n">
         <v>0.2296623005084529</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B145" s="3" t="n">
+      <c r="B145" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="C145" s="3" t="n">
+      <c r="C145" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D145" s="2" t="n">
+      <c r="D145" s="3" t="n">
         <v>0.2337491979196922</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B146" s="3" t="n">
+      <c r="B146" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="C146" s="3" t="n">
+      <c r="C146" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D146" s="2" t="n">
+      <c r="D146" s="3" t="n">
         <v>0.231401365204684</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B147" s="3" t="n">
+      <c r="B147" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="C147" s="3" t="n">
+      <c r="C147" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D147" s="3" t="n">
         <v>0.2344587233260903</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B148" s="3" t="n">
+      <c r="B148" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C148" s="3" t="n">
+      <c r="C148" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="D148" s="2" t="n">
+      <c r="D148" s="3" t="n">
         <v>0.2337935444507051</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B149" s="3" t="n">
+      <c r="B149" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="C149" s="3" t="n">
+      <c r="C149" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D149" s="3" t="n">
         <v>0.2313817636993311</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B150" s="3" t="n">
+      <c r="B150" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="C150" s="3" t="n">
+      <c r="C150" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="D150" s="2" t="n">
+      <c r="D150" s="3" t="n">
         <v>0.229288359236466</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B151" s="3" t="n">
+      <c r="B151" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="C151" s="3" t="n">
+      <c r="C151" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D151" s="2" t="n">
+      <c r="D151" s="3" t="n">
         <v>0.2296181638858062</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B152" s="3" t="n">
+      <c r="B152" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="C152" s="3" t="n">
+      <c r="C152" s="4" t="n">
         <v>6.1</v>
       </c>
-      <c r="D152" s="2" t="n">
+      <c r="D152" s="3" t="n">
         <v>0.2276679765581801</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B153" s="3" t="n">
+      <c r="B153" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="C153" s="3" t="n">
+      <c r="C153" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D153" s="2" t="n">
+      <c r="D153" s="3" t="n">
         <v>0.22818312215479</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B154" s="3" t="n">
+      <c r="B154" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="C154" s="3" t="n">
+      <c r="C154" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D154" s="3" t="n">
         <v>0.2273303699795831</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B155" s="3" t="n">
+      <c r="B155" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="C155" s="3" t="n">
+      <c r="C155" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D155" s="2" t="n">
+      <c r="D155" s="3" t="n">
         <v>0.2223982205270898</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B156" s="3" t="n">
+      <c r="B156" s="4" t="n">
         <v>25.7</v>
       </c>
-      <c r="C156" s="3" t="n">
+      <c r="C156" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D156" s="2" t="n">
+      <c r="D156" s="3" t="n">
         <v>0.2269996991041931</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B157" s="3" t="n">
+      <c r="B157" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="C157" s="3" t="n">
+      <c r="C157" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D157" s="3" t="n">
         <v>0.2307998998903195</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B158" s="3" t="n">
+      <c r="B158" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="C158" s="3" t="n">
+      <c r="C158" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D158" s="2" t="n">
+      <c r="D158" s="3" t="n">
         <v>0.2309106224989629</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B159" s="3" t="n">
+      <c r="B159" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="C159" s="3" t="n">
+      <c r="C159" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D159" s="2" t="n">
+      <c r="D159" s="3" t="n">
         <v>0.2313516735410197</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B160" s="3" t="n">
+      <c r="B160" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C160" s="3" t="n">
+      <c r="C160" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D160" s="2" t="n">
+      <c r="D160" s="3" t="n">
         <v>0.2306294483365661</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B161" s="3" t="n">
+      <c r="B161" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="C161" s="3" t="n">
+      <c r="C161" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D161" s="2" t="n">
+      <c r="D161" s="3" t="n">
         <v>0.2294983172850124</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B162" s="3" t="n">
+      <c r="B162" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="C162" s="3" t="n">
+      <c r="C162" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D162" s="2" t="n">
+      <c r="D162" s="3" t="n">
         <v>0.2287026976988926</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B163" s="3" t="n">
+      <c r="B163" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="C163" s="3" t="n">
+      <c r="C163" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D163" s="2" t="n">
+      <c r="D163" s="3" t="n">
         <v>0.2297852499560769</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B164" s="3" t="n">
+      <c r="B164" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="C164" s="3" t="n">
+      <c r="C164" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D164" s="2" t="n">
+      <c r="D164" s="3" t="n">
         <v>0.2319214393587778</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B165" s="3" t="n">
+      <c r="B165" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="C165" s="3" t="n">
+      <c r="C165" s="4" t="n">
         <v>5.6</v>
       </c>
-      <c r="D165" s="2" t="n">
+      <c r="D165" s="3" t="n">
         <v>0.2320130487636571</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B166" s="3" t="n">
+      <c r="B166" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="C166" s="3" t="n">
+      <c r="C166" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D166" s="3" t="n">
         <v>0.2307141182294245</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B167" s="3" t="n">
+      <c r="B167" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="C167" s="3" t="n">
+      <c r="C167" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D167" s="3" t="n">
         <v>0.2281525216296589</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B168" s="3" t="n">
+      <c r="B168" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="C168" s="3" t="n">
+      <c r="C168" s="4" t="n">
         <v>5.7</v>
       </c>
-      <c r="D168" s="2" t="n">
+      <c r="D168" s="3" t="n">
         <v>0.2336158570051581</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B169" s="3" t="n">
+      <c r="B169" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="C169" s="3" t="n">
+      <c r="C169" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="D169" s="2" t="n">
+      <c r="D169" s="3" t="n">
         <v>0.2378872739647667</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B170" s="3" t="n">
+      <c r="B170" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C170" s="3" t="n">
+      <c r="C170" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="D170" s="2" t="n">
+      <c r="D170" s="3" t="n">
         <v>0.2399049316696376</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n">
+      <c r="B171" s="4" t="n">
         <v>27.1</v>
       </c>
-      <c r="C171" s="3" t="n">
+      <c r="C171" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="D171" s="2" t="n">
+      <c r="D171" s="3" t="n">
         <v>0.242166066134934</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B172" s="3" t="n">
+      <c r="B172" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="C172" s="3" t="n">
+      <c r="C172" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="D172" s="2" t="n">
+      <c r="D172" s="3" t="n">
         <v>0.2426195938894051</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B173" s="3" t="n">
+      <c r="B173" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="C173" s="3" t="n">
+      <c r="C173" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="D173" s="2" t="n">
+      <c r="D173" s="3" t="n">
         <v>0.243827945819321</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B174" s="3" t="n">
+      <c r="B174" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="C174" s="3" t="n">
+      <c r="C174" s="4" t="n">
         <v>6.7</v>
       </c>
-      <c r="D174" s="2" t="n">
+      <c r="D174" s="3" t="n">
         <v>0.2435061603754021</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B175" s="3" t="n">
+      <c r="B175" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="C175" s="3" t="n">
+      <c r="C175" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D175" s="2" t="n">
+      <c r="D175" s="3" t="n">
         <v>0.2446972358539269</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B176" s="3" t="n">
+      <c r="B176" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="C176" s="3" t="n">
+      <c r="C176" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="D176" s="2" t="n">
+      <c r="D176" s="3" t="n">
         <v>0.2461147734487857</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B177" s="3" t="n">
+      <c r="B177" s="4" t="n">
         <v>27.9</v>
       </c>
-      <c r="C177" s="3" t="n">
+      <c r="C177" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="D177" s="2" t="n">
+      <c r="D177" s="3" t="n">
         <v>0.2481374902754657</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B178" s="3" t="n">
+      <c r="B178" s="4" t="n">
         <v>27.9</v>
       </c>
-      <c r="C178" s="3" t="n">
+      <c r="C178" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="D178" s="2" t="n">
+      <c r="D178" s="3" t="n">
         <v>0.2474370301084636</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B179" s="3" t="n">
+      <c r="B179" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="C179" s="3" t="n">
+      <c r="C179" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="D179" s="2" t="n">
+      <c r="D179" s="3" t="n">
         <v>0.2429340615449442</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B180" s="3" t="n">
+      <c r="B180" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="C180" s="3" t="n">
+      <c r="C180" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D180" s="2" t="n">
+      <c r="D180" s="3" t="n">
         <v>0.2473099105670328</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B181" s="3" t="n">
+      <c r="B181" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="C181" s="3" t="n">
+      <c r="C181" s="4" t="n">
         <v>7.4</v>
       </c>
-      <c r="D181" s="2" t="n">
+      <c r="D181" s="3" t="n">
         <v>0.2514431486763121</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B182" s="3" t="n">
+      <c r="B182" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="C182" s="3" t="n">
+      <c r="C182" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="D182" s="2" t="n">
+      <c r="D182" s="3" t="n">
         <v>0.2482803673368081</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B183" s="3" t="n">
+      <c r="B183" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="C183" s="3" t="n">
+      <c r="C183" s="4" t="n">
         <v>7.4</v>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D183" s="3" t="n">
         <v>0.2494966316847115</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B184" s="3" t="n">
+      <c r="B184" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="C184" s="3" t="n">
+      <c r="C184" s="4" t="n">
         <v>7.6</v>
       </c>
-      <c r="D184" s="2" t="n">
+      <c r="D184" s="3" t="n">
         <v>0.2480071538369883</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B185" s="3" t="n">
+      <c r="B185" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="C185" s="3" t="n">
+      <c r="C185" s="4" t="n">
         <v>7.4</v>
       </c>
-      <c r="D185" s="2" t="n">
-        <v>0.2450930472230976</v>
+      <c r="D185" s="3" t="n">
+        <v>0.2451654985621509</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B186" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="C186" s="3" t="n">
+      <c r="B186" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C186" s="4" t="n">
         <v>7.8</v>
       </c>
-      <c r="D186" s="2" t="n">
-        <v>0.2437716771500794</v>
+      <c r="D186" s="3" t="n">
+        <v>0.2437743249370702</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0.2445066181349704</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D186"/>
+  <autoFilter ref="A1:D187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>